--- a/FPS_Test/Assets/Excel/ExcelData.xlsx
+++ b/FPS_Test/Assets/Excel/ExcelData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\GitHub\game_team\FPS_Test\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA493052-355F-42B1-BB32-BC9887CA1744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C3738CD-A9AF-4A79-A8D4-31257FB53A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5010" yWindow="-13155" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5010" yWindow="-13155" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="common" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="83">
   <si>
     <t>id</t>
   </si>
@@ -110,32 +110,428 @@
   </si>
   <si>
     <t>price</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>1×1_head</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>小麦袋</t>
+    <rPh sb="0" eb="3">
+      <t>コムギブクロ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>水差し</t>
+    <rPh sb="0" eb="2">
+      <t>ミズサ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>草かんむり</t>
+    <rPh sb="0" eb="1">
+      <t>クサ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>銅の盃</t>
+    <rPh sb="0" eb="1">
+      <t>ドウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>サカズキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>銅の腕輪</t>
+    <rPh sb="0" eb="1">
+      <t>ドウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ウデワ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>木の器</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ウツワ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>壺</t>
+    <rPh sb="0" eb="1">
+      <t>ツボ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>錆びた金貨</t>
+    <rPh sb="0" eb="1">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キンカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>金貨の入った銅の盃</t>
+    <rPh sb="0" eb="2">
+      <t>キンカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ドウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>サカズキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>硬貨の入った袋</t>
+    <rPh sb="0" eb="2">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>フクロ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>おもちゃのティアラ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アンバー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>女神像</t>
+    <rPh sb="0" eb="3">
+      <t>メガミゾウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>小麦粉</t>
+    <rPh sb="0" eb="3">
+      <t>コムギコ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アクアマリン</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アメジスト</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>イエロートパーズ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>エメラルド</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クリスタルオパール</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クリスタルカフス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ゴールデントパーズ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>サファイアのロケット</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>シトリン</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ハートのネックレス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>パールリング</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ヒスイのリング</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ピンクスピネル</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ピンクハートジェム</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ブルーサファイア</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ブルートパーズ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ペリドット</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ルビーのネックレス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ルビーハート</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>水晶の指輪</t>
+    <rPh sb="0" eb="2">
+      <t>スイショウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ユビワ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>天色のブローチ</t>
+    <rPh sb="0" eb="1">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>イロ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ハートの指輪</t>
+    <rPh sb="4" eb="6">
+      <t>ユビワ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クリアダイヤモンド</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>トールの裁き</t>
+    <rPh sb="4" eb="5">
+      <t>サバ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ドラゴネイル</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ルビー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>王妃の髪飾り</t>
+    <rPh sb="0" eb="2">
+      <t>オウヒ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カミカザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>巨人の石</t>
+    <rPh sb="0" eb="2">
+      <t>キョジン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>イシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>虚栄の王冠</t>
+    <rPh sb="0" eb="2">
+      <t>キョエイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>オウカン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>翠玉の耳飾り</t>
+    <rPh sb="0" eb="2">
+      <t>スイギョク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ミミカザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>聖馬像</t>
+    <rPh sb="0" eb="1">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ウマ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ゾウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>太陽神の瞳</t>
+    <rPh sb="0" eb="3">
+      <t>タイヨウシン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヒトミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アレスの兜</t>
+    <rPh sb="4" eb="5">
+      <t>カブト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ウリエルの盃</t>
+    <rPh sb="5" eb="6">
+      <t>サカズキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>カドゥケウスのブローチ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ゴルゴンの盾</t>
+    <rPh sb="5" eb="6">
+      <t>タテ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>コルヌコピアの恵み</t>
+    <rPh sb="7" eb="8">
+      <t>メグ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>トライデント</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ヘルメスの靴</t>
+    <rPh sb="5" eb="6">
+      <t>クツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>月光泡影</t>
+    <rPh sb="0" eb="2">
+      <t>ゲッコウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>アワ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カゲ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>神々のブーツ</t>
+    <rPh sb="0" eb="2">
+      <t>カミガミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>神罰の枷</t>
+    <rPh sb="0" eb="2">
+      <t>シンバツ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カセ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>世界樹のハープ</t>
+    <rPh sb="0" eb="3">
+      <t>セカイジュ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>天翔弓</t>
+    <rPh sb="0" eb="2">
+      <t>テンショウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ユミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>神々の腕輪</t>
+    <rPh sb="0" eb="2">
+      <t>カミガミ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ウデワ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
@@ -171,10 +567,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -494,10 +889,10 @@
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4.625" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="17.25" customWidth="1"/>
     <col min="3" max="4" width="8.625" customWidth="1"/>
     <col min="5" max="5" width="13.375" customWidth="1"/>
-    <col min="6" max="6" width="16.875" customWidth="1"/>
+    <col min="6" max="6" width="17.625" customWidth="1"/>
     <col min="7" max="7" width="14.625" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="1025" width="8.625" customWidth="1"/>
@@ -546,7 +941,7 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>15</v>
@@ -576,7 +971,7 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -592,19 +987,397 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="5" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="6" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="7" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="8" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="10" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="11" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="12" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="13" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="14" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="15" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="16" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="4" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4" t="str">
+        <f t="shared" ref="H4:H15" si="0">IF(G4=0,"Helmet",IF(G4=1,"Armor",IF(G4=2,"Gauntlet",IF(G4=3,"Shoes",IF(G4=4,"Weapon","None")))))</f>
+        <v>None</v>
+      </c>
+      <c r="I4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>15</v>
+      </c>
+      <c r="F9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="H10" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+      <c r="F11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+      <c r="H11" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I11">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+      <c r="H12" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+      <c r="H13" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I13">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+      <c r="H14" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I15">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <f>100-SUM(E2:E15)</f>
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
+        <v>36</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+      <c r="H16" t="str">
+        <f>IF(G16=0,"Helmet",IF(G16=1,"Armor",IF(G16=2,"Gauntlet",IF(G16=3,"Shoes",IF(G16=4,"Weapon","None")))))</f>
+        <v>None</v>
+      </c>
+      <c r="I16">
+        <v>50</v>
+      </c>
+    </row>
     <row r="17" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="18" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="19" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -688,7 +1461,7 @@
     <row r="97" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="98" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
-  <phoneticPr fontId="3"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
@@ -696,14 +1469,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
-    <col min="2" max="2" width="14.5" customWidth="1"/>
+    <col min="2" max="2" width="19.875" customWidth="1"/>
     <col min="3" max="4" width="8.625" customWidth="1"/>
     <col min="5" max="5" width="10.375" customWidth="1"/>
-    <col min="6" max="6" width="13.25" customWidth="1"/>
+    <col min="6" max="6" width="19.625" customWidth="1"/>
     <col min="7" max="7" width="10.125" customWidth="1"/>
     <col min="8" max="8" width="12.75" customWidth="1"/>
     <col min="9" max="1025" width="8.625" customWidth="1"/>
@@ -752,7 +1525,7 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>17</v>
@@ -782,7 +1555,7 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -798,8 +1571,669 @@
         <v>80</v>
       </c>
     </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4" t="str">
+        <f t="shared" ref="H4:H25" si="0">IF(G4=0,"Helmet",IF(G4=1,"Armor",IF(G4=2,"Gauntlet",IF(G4=3,"Shoes",IF(G4=4,"Weapon","None")))))</f>
+        <v>None</v>
+      </c>
+      <c r="I4">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I5">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I6">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I7">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+      <c r="F9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I9">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="H10" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I10">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>5</v>
+      </c>
+      <c r="F11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+      <c r="H11" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I11">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>5</v>
+      </c>
+      <c r="F12" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+      <c r="H12" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I12">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>5</v>
+      </c>
+      <c r="F13" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+      <c r="H13" t="str">
+        <f>IF(G13=0,"Helmet",IF(G13=1,"Armor",IF(G13=2,"Gauntlet",IF(G13=3,"Shoes",IF(G13=4,"Weapon","None")))))</f>
+        <v>None</v>
+      </c>
+      <c r="I13">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+      <c r="H14" t="str">
+        <f>IF(G14=0,"Helmet",IF(G14=1,"Armor",IF(G14=2,"Gauntlet",IF(G14=3,"Shoes",IF(G14=4,"Weapon","None")))))</f>
+        <v>None</v>
+      </c>
+      <c r="I14">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>5</v>
+      </c>
+      <c r="F15" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I15">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>5</v>
+      </c>
+      <c r="F16" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+      <c r="H16" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I16">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>5</v>
+      </c>
+      <c r="F17" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+      <c r="H17" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I17">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>5</v>
+      </c>
+      <c r="F18" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+      <c r="H18" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I18">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>5</v>
+      </c>
+      <c r="F19" t="s">
+        <v>52</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+      <c r="H19" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I19">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>5</v>
+      </c>
+      <c r="F20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+      <c r="H20" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I20">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>5</v>
+      </c>
+      <c r="F21" t="s">
+        <v>54</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+      <c r="H21" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I21">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>5</v>
+      </c>
+      <c r="F22" t="s">
+        <v>55</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+      <c r="H22" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I22">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>5</v>
+      </c>
+      <c r="F23" t="s">
+        <v>56</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
+      </c>
+      <c r="H23" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I23">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>5</v>
+      </c>
+      <c r="F24" t="s">
+        <v>57</v>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+      <c r="H24" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I24">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <f>100-SUM(E2:E24)</f>
+        <v>-15</v>
+      </c>
+      <c r="F25" t="s">
+        <v>58</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+      <c r="H25" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I25">
+        <v>300</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="3"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -807,11 +2241,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
-    <col min="2" max="2" width="12.875" customWidth="1"/>
+    <col min="2" max="2" width="17.75" customWidth="1"/>
     <col min="3" max="4" width="8.625" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="17.5" customWidth="1"/>
@@ -864,7 +2298,7 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>19</v>
@@ -877,7 +2311,7 @@
         <v>Shoes</v>
       </c>
       <c r="I2">
-        <v>250</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
@@ -894,7 +2328,7 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
         <v>20</v>
@@ -910,8 +2344,309 @@
         <v>500</v>
       </c>
     </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4" t="str">
+        <f t="shared" ref="H4:H13" si="0">IF(G4=0,"Helmet",IF(G4=1,"Armor",IF(G4=2,"Gauntlet",IF(G4=3,"Shoes",IF(G4=4,"Weapon","None")))))</f>
+        <v>None</v>
+      </c>
+      <c r="I4">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I5">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I6">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I7">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I8">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+      <c r="F9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I9">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="H10" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I10">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>5</v>
+      </c>
+      <c r="F11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+      <c r="H11" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I11">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12">
+        <v>5</v>
+      </c>
+      <c r="F12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+      <c r="H12" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I12">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <f>100-SUM(E2:E12)</f>
+        <v>45</v>
+      </c>
+      <c r="F13" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+      <c r="H13" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I13">
+        <v>3000</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="3"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -919,14 +2654,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
-    <col min="2" max="2" width="11.375" customWidth="1"/>
+    <col min="2" max="2" width="21.75" customWidth="1"/>
     <col min="3" max="4" width="8.625" customWidth="1"/>
     <col min="5" max="5" width="11.375" customWidth="1"/>
-    <col min="6" max="6" width="13.75" customWidth="1"/>
+    <col min="6" max="6" width="20.75" customWidth="1"/>
     <col min="7" max="7" width="15.875" customWidth="1"/>
     <col min="8" max="8" width="12.5" customWidth="1"/>
     <col min="9" max="10" width="10.25" customWidth="1"/>
@@ -976,7 +2711,7 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>21</v>
@@ -992,11 +2727,399 @@
         <v>1000</v>
       </c>
     </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3" t="str">
+        <f t="shared" ref="H3:H15" si="0">IF(G3=0,"Helmet",IF(G3=1,"Armor",IF(G3=2,"Gauntlet",IF(G3=3,"Shoes",IF(G3=4,"Weapon","None")))))</f>
+        <v>None</v>
+      </c>
+      <c r="I3">
+        <v>3400</v>
+      </c>
+    </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="G4" s="1"/>
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I4">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I5">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I6">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I7">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I8">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+      <c r="F9" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I9">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="H10" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I10">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>5</v>
+      </c>
+      <c r="F11" t="s">
+        <v>78</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+      <c r="H11" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I11">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>5</v>
+      </c>
+      <c r="F12" t="s">
+        <v>82</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+      <c r="H12" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I12">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>5</v>
+      </c>
+      <c r="F13" t="s">
+        <v>79</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+      <c r="H13" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I13">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>3</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14" t="s">
+        <v>80</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+      <c r="H14" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I14">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>3</v>
+      </c>
+      <c r="E15">
+        <f>100-SUM(E2:E14)</f>
+        <v>39</v>
+      </c>
+      <c r="F15" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I15">
+        <v>4000</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
@@ -1016,7 +3139,7 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C1" t="s">
@@ -1031,16 +3154,16 @@
       <c r="F1" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1063,17 +3186,17 @@
       <c r="F2">
         <v>6</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <f>100 - (H2+I2+J2)</f>
         <v>89</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="2">
         <v>10</v>
       </c>
-      <c r="I2" s="3">
-        <v>1</v>
-      </c>
-      <c r="J2" s="3">
+      <c r="I2" s="2">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1096,17 +3219,17 @@
       <c r="F3">
         <v>7</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="2">
         <f>100 - (H3+I3+J3)</f>
         <v>74</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="2">
         <v>20</v>
       </c>
-      <c r="I3" s="3">
-        <v>5</v>
-      </c>
-      <c r="J3" s="3">
+      <c r="I3" s="2">
+        <v>5</v>
+      </c>
+      <c r="J3" s="2">
         <v>1</v>
       </c>
     </row>
@@ -1129,17 +3252,17 @@
       <c r="F4">
         <v>8</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <f>100 - (H4+I4+J4)</f>
         <v>60</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="2">
         <v>30</v>
       </c>
-      <c r="I4" s="3">
-        <v>5</v>
-      </c>
-      <c r="J4" s="3">
+      <c r="I4" s="2">
+        <v>5</v>
+      </c>
+      <c r="J4" s="2">
         <v>5</v>
       </c>
     </row>
@@ -1162,22 +3285,22 @@
       <c r="F5">
         <v>9</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <f>100 - (H5+I5+J5)</f>
         <v>45</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <v>40</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="2">
         <v>10</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="2">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3"/>
+  <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="G1:J5">
     <cfRule type="colorScale" priority="2">
       <colorScale>

--- a/FPS_Test/Assets/Excel/ExcelData.xlsx
+++ b/FPS_Test/Assets/Excel/ExcelData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\GitHub\game_team\FPS_Test\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C3738CD-A9AF-4A79-A8D4-31257FB53A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED31C17-5262-4F56-983B-9D5EFF860C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5010" yWindow="-13155" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3390" yWindow="2340" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="common" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="100">
   <si>
     <t>id</t>
   </si>
@@ -517,6 +517,110 @@
     </rPh>
     <rPh sb="3" eb="5">
       <t>ウデワ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Common短剣</t>
+    <rPh sb="6" eb="8">
+      <t>タンケン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Common大剣</t>
+    <rPh sb="6" eb="8">
+      <t>タイケン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Commonメイス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Common杖</t>
+    <rPh sb="6" eb="7">
+      <t>ツエ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Common短剣</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Rare短剣</t>
+    <rPh sb="4" eb="6">
+      <t>タンケン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Rare大剣</t>
+    <rPh sb="4" eb="6">
+      <t>タイケン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Rareメイス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Rare杖</t>
+    <rPh sb="4" eb="5">
+      <t>ツエ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Unique短剣</t>
+    <rPh sb="6" eb="8">
+      <t>タンケン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Unique大剣</t>
+    <rPh sb="6" eb="8">
+      <t>タイケン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Uniqueメイス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Unique杖</t>
+    <rPh sb="6" eb="7">
+      <t>ツエ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Legendary短剣</t>
+    <rPh sb="9" eb="11">
+      <t>タンケン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Legendary大剣</t>
+    <rPh sb="9" eb="11">
+      <t>タイケン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Legendaryメイス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Legendary杖</t>
+    <rPh sb="9" eb="10">
+      <t>ツエ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -885,7 +989,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I98"/>
+  <dimension ref="A1:I102"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4.625" customWidth="1"/>
@@ -992,7 +1096,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>83</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1001,20 +1105,20 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H4" t="str">
-        <f t="shared" ref="H4:H15" si="0">IF(G4=0,"Helmet",IF(G4=1,"Armor",IF(G4=2,"Gauntlet",IF(G4=3,"Shoes",IF(G4=4,"Weapon","None")))))</f>
-        <v>None</v>
+        <f t="shared" ref="H4:H7" si="0">IF(G4=0,"Helmet",IF(G4=1,"Armor",IF(G4=2,"Gauntlet",IF(G4=3,"Shoes",IF(G4=4,"Weapon","None")))))</f>
+        <v>Weapon</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1022,29 +1126,29 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5" t="str">
         <f t="shared" si="0"/>
-        <v>None</v>
+        <v>Weapon</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1052,67 +1156,67 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6" t="str">
         <f t="shared" si="0"/>
-        <v>None</v>
+        <v>Weapon</v>
       </c>
       <c r="I6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="0"/>
-        <v>None</v>
+        <v>Weapon</v>
       </c>
       <c r="I7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1121,20 +1225,20 @@
         <v>1</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G8">
         <v>5</v>
       </c>
       <c r="H8" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="H8:H19" si="1">IF(G8=0,"Helmet",IF(G8=1,"Armor",IF(G8=2,"Gauntlet",IF(G8=3,"Shoes",IF(G8=4,"Weapon","None")))))</f>
         <v>None</v>
       </c>
       <c r="I8">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1142,29 +1246,29 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G9">
         <v>5</v>
       </c>
       <c r="H9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1172,29 +1276,29 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G10">
         <v>5</v>
       </c>
       <c r="H10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I10">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1202,7 +1306,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1211,20 +1315,20 @@
         <v>1</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G11">
         <v>5</v>
       </c>
       <c r="H11" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I11">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1232,7 +1336,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1241,20 +1345,20 @@
         <v>1</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G12">
         <v>5</v>
       </c>
       <c r="H12" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I12">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1262,7 +1366,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1271,20 +1375,20 @@
         <v>1</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G13">
         <v>5</v>
       </c>
       <c r="H13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I13">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1292,29 +1396,29 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G14">
         <v>5</v>
       </c>
       <c r="H14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I14">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1322,7 +1426,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1331,20 +1435,20 @@
         <v>1</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G15">
         <v>5</v>
       </c>
       <c r="H15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I15">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1352,48 +1456,164 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+      <c r="H16" t="str">
+        <f t="shared" si="1"/>
+        <v>None</v>
+      </c>
+      <c r="I16">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+      <c r="H17" t="str">
+        <f t="shared" si="1"/>
+        <v>None</v>
+      </c>
+      <c r="I17">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+      <c r="H18" t="str">
+        <f t="shared" si="1"/>
+        <v>None</v>
+      </c>
+      <c r="I18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+      <c r="H19" t="str">
+        <f t="shared" si="1"/>
+        <v>None</v>
+      </c>
+      <c r="I19">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
         <v>36</v>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
-      <c r="E16">
-        <f>100-SUM(E2:E15)</f>
-        <v>12</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20">
+        <f>100-SUM(E2:E19)</f>
+        <v>4</v>
+      </c>
+      <c r="F20" t="s">
         <v>36</v>
       </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-      <c r="H16" t="str">
-        <f>IF(G16=0,"Helmet",IF(G16=1,"Armor",IF(G16=2,"Gauntlet",IF(G16=3,"Shoes",IF(G16=4,"Weapon","None")))))</f>
-        <v>None</v>
-      </c>
-      <c r="I16">
+      <c r="G20">
+        <v>5</v>
+      </c>
+      <c r="H20" t="str">
+        <f>IF(G20=0,"Helmet",IF(G20=1,"Armor",IF(G20=2,"Gauntlet",IF(G20=3,"Shoes",IF(G20=4,"Weapon","None")))))</f>
+        <v>None</v>
+      </c>
+      <c r="I20">
         <v>50</v>
       </c>
     </row>
-    <row r="17" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="18" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="19" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="20" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="21" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="22" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="23" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="24" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="25" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="26" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="27" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="28" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="29" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="30" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="31" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="32" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="21" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="22" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="23" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="24" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="25" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="26" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="27" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="28" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="29" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="30" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="31" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="32" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="33" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="34" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="35" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -1460,6 +1680,10 @@
     <row r="96" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="97" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="98" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="99" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="100" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="101" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="102" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -1469,7 +1693,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
@@ -1576,7 +1800,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1585,20 +1809,20 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H4" t="str">
-        <f t="shared" ref="H4:H25" si="0">IF(G4=0,"Helmet",IF(G4=1,"Armor",IF(G4=2,"Gauntlet",IF(G4=3,"Shoes",IF(G4=4,"Weapon","None")))))</f>
-        <v>None</v>
+        <f t="shared" ref="H4:H7" si="0">IF(G4=0,"Helmet",IF(G4=1,"Armor",IF(G4=2,"Gauntlet",IF(G4=3,"Shoes",IF(G4=4,"Weapon","None")))))</f>
+        <v>Weapon</v>
       </c>
       <c r="I4">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.4">
@@ -1606,29 +1830,29 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5" t="str">
         <f t="shared" si="0"/>
-        <v>None</v>
+        <v>Weapon</v>
       </c>
       <c r="I5">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
@@ -1636,29 +1860,29 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6" t="str">
         <f t="shared" si="0"/>
-        <v>None</v>
+        <v>Weapon</v>
       </c>
       <c r="I6">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.4">
@@ -1666,29 +1890,29 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="0"/>
-        <v>None</v>
+        <v>Weapon</v>
       </c>
       <c r="I7">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.4">
@@ -1696,7 +1920,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1705,20 +1929,20 @@
         <v>1</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G8">
         <v>5</v>
       </c>
       <c r="H8" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="H8:H29" si="1">IF(G8=0,"Helmet",IF(G8=1,"Armor",IF(G8=2,"Gauntlet",IF(G8=3,"Shoes",IF(G8=4,"Weapon","None")))))</f>
         <v>None</v>
       </c>
       <c r="I8">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.4">
@@ -1726,7 +1950,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1735,20 +1959,20 @@
         <v>1</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G9">
         <v>5</v>
       </c>
       <c r="H9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I9">
-        <v>230</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.4">
@@ -1756,7 +1980,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1765,20 +1989,20 @@
         <v>1</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G10">
         <v>5</v>
       </c>
       <c r="H10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I10">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
@@ -1786,7 +2010,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1795,20 +2019,20 @@
         <v>1</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G11">
         <v>5</v>
       </c>
       <c r="H11" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I11">
-        <v>230</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.4">
@@ -1816,7 +2040,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1825,20 +2049,20 @@
         <v>1</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G12">
         <v>5</v>
       </c>
       <c r="H12" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I12">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.4">
@@ -1846,7 +2070,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1855,20 +2079,20 @@
         <v>1</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G13">
         <v>5</v>
       </c>
       <c r="H13" t="str">
-        <f>IF(G13=0,"Helmet",IF(G13=1,"Armor",IF(G13=2,"Gauntlet",IF(G13=3,"Shoes",IF(G13=4,"Weapon","None")))))</f>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I13">
-        <v>200</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.4">
@@ -1876,7 +2100,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1885,20 +2109,20 @@
         <v>1</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="G14">
         <v>5</v>
       </c>
       <c r="H14" t="str">
-        <f>IF(G14=0,"Helmet",IF(G14=1,"Armor",IF(G14=2,"Gauntlet",IF(G14=3,"Shoes",IF(G14=4,"Weapon","None")))))</f>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I14">
-        <v>170</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
@@ -1906,7 +2130,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1915,20 +2139,20 @@
         <v>1</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G15">
         <v>5</v>
       </c>
       <c r="H15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I15">
-        <v>170</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.4">
@@ -1936,7 +2160,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -1945,20 +2169,20 @@
         <v>1</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G16">
         <v>5</v>
       </c>
       <c r="H16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I16">
-        <v>170</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.4">
@@ -1966,7 +2190,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -1975,20 +2199,20 @@
         <v>1</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G17">
         <v>5</v>
       </c>
       <c r="H17" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(G17=0,"Helmet",IF(G17=1,"Armor",IF(G17=2,"Gauntlet",IF(G17=3,"Shoes",IF(G17=4,"Weapon","None")))))</f>
         <v>None</v>
       </c>
       <c r="I17">
-        <v>130</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
@@ -1996,7 +2220,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -2005,20 +2229,20 @@
         <v>1</v>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G18">
         <v>5</v>
       </c>
       <c r="H18" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(G18=0,"Helmet",IF(G18=1,"Armor",IF(G18=2,"Gauntlet",IF(G18=3,"Shoes",IF(G18=4,"Weapon","None")))))</f>
         <v>None</v>
       </c>
       <c r="I18">
-        <v>120</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.4">
@@ -2026,7 +2250,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -2035,20 +2259,20 @@
         <v>1</v>
       </c>
       <c r="E19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G19">
         <v>5</v>
       </c>
       <c r="H19" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I19">
-        <v>220</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.4">
@@ -2056,7 +2280,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -2065,20 +2289,20 @@
         <v>1</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G20">
         <v>5</v>
       </c>
       <c r="H20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I20">
-        <v>150</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.4">
@@ -2086,7 +2310,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -2095,20 +2319,20 @@
         <v>1</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F21" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G21">
         <v>5</v>
       </c>
       <c r="H21" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I21">
-        <v>150</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.4">
@@ -2116,7 +2340,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -2125,20 +2349,20 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G22">
         <v>5</v>
       </c>
       <c r="H22" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I22">
-        <v>180</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.4">
@@ -2146,7 +2370,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -2155,20 +2379,20 @@
         <v>1</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G23">
         <v>5</v>
       </c>
       <c r="H23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I23">
-        <v>150</v>
+        <v>220</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.4">
@@ -2176,7 +2400,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -2185,20 +2409,20 @@
         <v>1</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G24">
         <v>5</v>
       </c>
       <c r="H24" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I24">
-        <v>170</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.4">
@@ -2206,29 +2430,149 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>3</v>
+      </c>
+      <c r="F25" t="s">
+        <v>54</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+      <c r="H25" t="str">
+        <f t="shared" si="1"/>
+        <v>None</v>
+      </c>
+      <c r="I25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>3</v>
+      </c>
+      <c r="F26" t="s">
+        <v>55</v>
+      </c>
+      <c r="G26">
+        <v>5</v>
+      </c>
+      <c r="H26" t="str">
+        <f t="shared" si="1"/>
+        <v>None</v>
+      </c>
+      <c r="I26">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>3</v>
+      </c>
+      <c r="F27" t="s">
+        <v>56</v>
+      </c>
+      <c r="G27">
+        <v>5</v>
+      </c>
+      <c r="H27" t="str">
+        <f t="shared" si="1"/>
+        <v>None</v>
+      </c>
+      <c r="I27">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>3</v>
+      </c>
+      <c r="F28" t="s">
+        <v>57</v>
+      </c>
+      <c r="G28">
+        <v>5</v>
+      </c>
+      <c r="H28" t="str">
+        <f t="shared" si="1"/>
+        <v>None</v>
+      </c>
+      <c r="I28">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
         <v>58</v>
       </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-      <c r="E25">
-        <f>100-SUM(E2:E24)</f>
-        <v>-15</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <f>100-SUM(E2:E28)</f>
+        <v>19</v>
+      </c>
+      <c r="F29" t="s">
         <v>58</v>
       </c>
-      <c r="G25">
-        <v>5</v>
-      </c>
-      <c r="H25" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I25">
+      <c r="G29">
+        <v>5</v>
+      </c>
+      <c r="H29" t="str">
+        <f t="shared" si="1"/>
+        <v>None</v>
+      </c>
+      <c r="I29">
         <v>300</v>
       </c>
     </row>
@@ -2241,7 +2585,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
@@ -2349,7 +2693,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -2358,17 +2702,17 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H4" t="str">
-        <f t="shared" ref="H4:H13" si="0">IF(G4=0,"Helmet",IF(G4=1,"Armor",IF(G4=2,"Gauntlet",IF(G4=3,"Shoes",IF(G4=4,"Weapon","None")))))</f>
-        <v>None</v>
+        <f t="shared" ref="H4:H7" si="0">IF(G4=0,"Helmet",IF(G4=1,"Armor",IF(G4=2,"Gauntlet",IF(G4=3,"Shoes",IF(G4=4,"Weapon","None")))))</f>
+        <v>Weapon</v>
       </c>
       <c r="I4">
         <v>500</v>
@@ -2379,29 +2723,29 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5" t="str">
         <f t="shared" si="0"/>
-        <v>None</v>
+        <v>Weapon</v>
       </c>
       <c r="I5">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
@@ -2409,29 +2753,29 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6" t="str">
         <f t="shared" si="0"/>
-        <v>None</v>
+        <v>Weapon</v>
       </c>
       <c r="I6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.4">
@@ -2439,29 +2783,29 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="0"/>
-        <v>None</v>
+        <v>Weapon</v>
       </c>
       <c r="I7">
-        <v>1700</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.4">
@@ -2469,7 +2813,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -2481,17 +2825,17 @@
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G8">
         <v>5</v>
       </c>
       <c r="H8" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="H8:H17" si="1">IF(G8=0,"Helmet",IF(G8=1,"Armor",IF(G8=2,"Gauntlet",IF(G8=3,"Shoes",IF(G8=4,"Weapon","None")))))</f>
         <v>None</v>
       </c>
       <c r="I8">
-        <v>620</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.4">
@@ -2499,7 +2843,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -2511,17 +2855,17 @@
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G9">
         <v>5</v>
       </c>
       <c r="H9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I9">
-        <v>1500</v>
+        <v>800</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.4">
@@ -2529,7 +2873,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -2541,17 +2885,17 @@
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G10">
         <v>5</v>
       </c>
       <c r="H10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I10">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
@@ -2559,29 +2903,29 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11">
         <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G11">
         <v>5</v>
       </c>
       <c r="H11" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I11">
-        <v>800</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.4">
@@ -2589,29 +2933,29 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12">
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G12">
         <v>5</v>
       </c>
       <c r="H12" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I12">
-        <v>1200</v>
+        <v>620</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.4">
@@ -2619,29 +2963,149 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>5</v>
+      </c>
+      <c r="F13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+      <c r="H13" t="str">
+        <f t="shared" si="1"/>
+        <v>None</v>
+      </c>
+      <c r="I13">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+      <c r="H14" t="str">
+        <f t="shared" si="1"/>
+        <v>None</v>
+      </c>
+      <c r="I14">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>5</v>
+      </c>
+      <c r="F15" t="s">
+        <v>67</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15" t="str">
+        <f t="shared" si="1"/>
+        <v>None</v>
+      </c>
+      <c r="I15">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>5</v>
+      </c>
+      <c r="F16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+      <c r="H16" t="str">
+        <f t="shared" si="1"/>
+        <v>None</v>
+      </c>
+      <c r="I16">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
         <v>69</v>
       </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-      <c r="D13">
-        <v>2</v>
-      </c>
-      <c r="E13">
-        <f>100-SUM(E2:E12)</f>
-        <v>45</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17">
+        <f>100-SUM(E2:E16)</f>
+        <v>37</v>
+      </c>
+      <c r="F17" t="s">
         <v>69</v>
       </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-      <c r="H13" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I13">
+      <c r="G17">
+        <v>5</v>
+      </c>
+      <c r="H17" t="str">
+        <f t="shared" si="1"/>
+        <v>None</v>
+      </c>
+      <c r="I17">
         <v>3000</v>
       </c>
     </row>
@@ -2654,7 +3118,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
@@ -2732,29 +3196,29 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H3" t="str">
-        <f t="shared" ref="H3:H15" si="0">IF(G3=0,"Helmet",IF(G3=1,"Armor",IF(G3=2,"Gauntlet",IF(G3=3,"Shoes",IF(G3=4,"Weapon","None")))))</f>
-        <v>None</v>
+        <f t="shared" ref="H3:H6" si="0">IF(G3=0,"Helmet",IF(G3=1,"Armor",IF(G3=2,"Gauntlet",IF(G3=3,"Shoes",IF(G3=4,"Weapon","None")))))</f>
+        <v>Weapon</v>
       </c>
       <c r="I3">
-        <v>3400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
@@ -2762,29 +3226,29 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H4" t="str">
         <f t="shared" si="0"/>
-        <v>None</v>
+        <v>Weapon</v>
       </c>
       <c r="I4">
-        <v>830</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.4">
@@ -2792,29 +3256,29 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5" t="str">
         <f t="shared" si="0"/>
-        <v>None</v>
+        <v>Weapon</v>
       </c>
       <c r="I5">
-        <v>900</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
@@ -2822,29 +3286,29 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6" t="str">
         <f t="shared" si="0"/>
-        <v>None</v>
+        <v>Weapon</v>
       </c>
       <c r="I6">
-        <v>3500</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.4">
@@ -2852,29 +3316,29 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7">
         <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G7">
         <v>5</v>
       </c>
       <c r="H7" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="H7:H19" si="1">IF(G7=0,"Helmet",IF(G7=1,"Armor",IF(G7=2,"Gauntlet",IF(G7=3,"Shoes",IF(G7=4,"Weapon","None")))))</f>
         <v>None</v>
       </c>
       <c r="I7">
-        <v>1100</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.4">
@@ -2882,29 +3346,29 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8">
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G8">
         <v>5</v>
       </c>
       <c r="H8" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I8">
-        <v>2700</v>
+        <v>830</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.4">
@@ -2912,7 +3376,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -2924,17 +3388,17 @@
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G9">
         <v>5</v>
       </c>
       <c r="H9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I9">
-        <v>810</v>
+        <v>900</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.4">
@@ -2942,29 +3406,29 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G10">
         <v>5</v>
       </c>
       <c r="H10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I10">
-        <v>1500</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
@@ -2972,29 +3436,29 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G11">
         <v>5</v>
       </c>
       <c r="H11" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I11">
-        <v>3300</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.4">
@@ -3002,29 +3466,29 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12">
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G12">
         <v>5</v>
       </c>
       <c r="H12" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I12">
-        <v>800</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.4">
@@ -3032,10 +3496,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -3044,17 +3508,17 @@
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G13">
         <v>5</v>
       </c>
       <c r="H13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I13">
-        <v>1700</v>
+        <v>810</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.4">
@@ -3062,29 +3526,29 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G14">
         <v>5</v>
       </c>
       <c r="H14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I14">
-        <v>10000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
@@ -3092,29 +3556,149 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15">
+        <v>5</v>
+      </c>
+      <c r="F15" t="s">
+        <v>78</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15" t="str">
+        <f t="shared" si="1"/>
+        <v>None</v>
+      </c>
+      <c r="I15">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>5</v>
+      </c>
+      <c r="F16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+      <c r="H16" t="str">
+        <f t="shared" si="1"/>
+        <v>None</v>
+      </c>
+      <c r="I16">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>5</v>
+      </c>
+      <c r="F17" t="s">
+        <v>79</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+      <c r="H17" t="str">
+        <f t="shared" si="1"/>
+        <v>None</v>
+      </c>
+      <c r="I17">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>80</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+      <c r="H18" t="str">
+        <f t="shared" si="1"/>
+        <v>None</v>
+      </c>
+      <c r="I18">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
         <v>81</v>
       </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>3</v>
-      </c>
-      <c r="E15">
-        <f>100-SUM(E2:E14)</f>
-        <v>39</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="E19">
+        <f>100-SUM(E2:E18)</f>
+        <v>31</v>
+      </c>
+      <c r="F19" t="s">
         <v>81</v>
       </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-      <c r="H15" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I15">
+      <c r="G19">
+        <v>5</v>
+      </c>
+      <c r="H19" t="str">
+        <f t="shared" si="1"/>
+        <v>None</v>
+      </c>
+      <c r="I19">
         <v>4000</v>
       </c>
     </row>

--- a/FPS_Test/Assets/Excel/ExcelData.xlsx
+++ b/FPS_Test/Assets/Excel/ExcelData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\GitHub\game_team\FPS_Test\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED31C17-5262-4F56-983B-9D5EFF860C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FF4A75-58CD-4335-90A0-DF6AFD670DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3390" yWindow="2340" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3390" yWindow="-13860" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="common" sheetId="1" r:id="rId1"/>
@@ -185,22 +185,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>金貨の入った銅の盃</t>
-    <rPh sb="0" eb="2">
-      <t>キンカ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ハイ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ドウ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>サカズキ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>硬貨の入った袋</t>
     <rPh sb="0" eb="2">
       <t>コウカ</t>
@@ -229,13 +213,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>小麦粉</t>
-    <rPh sb="0" eb="3">
-      <t>コムギコ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>アクアマリン</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -621,6 +598,32 @@
     <t>Legendary杖</t>
     <rPh sb="9" eb="10">
       <t>ツエ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>小麦袋</t>
+    <rPh sb="0" eb="2">
+      <t>コムギ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ブクロ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>硬貨の入った銅の盃</t>
+    <rPh sb="0" eb="2">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ドウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>サカズキ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1096,7 +1099,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1108,7 +1111,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1126,7 +1129,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1138,7 +1141,7 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -1156,7 +1159,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1168,7 +1171,7 @@
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -1186,7 +1189,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1198,7 +1201,7 @@
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G7">
         <v>4</v>
@@ -1216,7 +1219,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1456,7 +1459,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -1468,7 +1471,7 @@
         <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -1486,7 +1489,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -1498,7 +1501,7 @@
         <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -1516,7 +1519,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1528,7 +1531,7 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -1546,7 +1549,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1558,7 +1561,7 @@
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -1576,7 +1579,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1589,7 +1592,7 @@
         <v>4</v>
       </c>
       <c r="F20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -1800,7 +1803,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1812,7 +1815,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1830,7 +1833,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1842,7 +1845,7 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -1860,7 +1863,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1872,7 +1875,7 @@
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -1890,7 +1893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1902,7 +1905,7 @@
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G7">
         <v>4</v>
@@ -1920,7 +1923,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1932,7 +1935,7 @@
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -1950,7 +1953,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1962,7 +1965,7 @@
         <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -1980,7 +1983,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1992,7 +1995,7 @@
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -2010,7 +2013,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -2022,7 +2025,7 @@
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -2040,7 +2043,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -2052,7 +2055,7 @@
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -2070,7 +2073,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -2082,7 +2085,7 @@
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -2100,7 +2103,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -2112,7 +2115,7 @@
         <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -2130,7 +2133,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -2142,7 +2145,7 @@
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -2160,7 +2163,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -2172,7 +2175,7 @@
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -2190,7 +2193,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -2202,7 +2205,7 @@
         <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -2220,7 +2223,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -2232,7 +2235,7 @@
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -2250,7 +2253,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -2262,7 +2265,7 @@
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -2280,7 +2283,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -2292,7 +2295,7 @@
         <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -2310,7 +2313,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -2322,7 +2325,7 @@
         <v>3</v>
       </c>
       <c r="F21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -2340,7 +2343,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -2352,7 +2355,7 @@
         <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -2370,7 +2373,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -2382,7 +2385,7 @@
         <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G23">
         <v>5</v>
@@ -2400,7 +2403,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -2412,7 +2415,7 @@
         <v>3</v>
       </c>
       <c r="F24" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G24">
         <v>5</v>
@@ -2430,7 +2433,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -2442,7 +2445,7 @@
         <v>3</v>
       </c>
       <c r="F25" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G25">
         <v>5</v>
@@ -2460,7 +2463,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -2472,7 +2475,7 @@
         <v>3</v>
       </c>
       <c r="F26" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G26">
         <v>5</v>
@@ -2490,7 +2493,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -2502,7 +2505,7 @@
         <v>3</v>
       </c>
       <c r="F27" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -2520,7 +2523,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -2532,7 +2535,7 @@
         <v>3</v>
       </c>
       <c r="F28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G28">
         <v>5</v>
@@ -2550,7 +2553,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -2563,7 +2566,7 @@
         <v>19</v>
       </c>
       <c r="F29" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G29">
         <v>5</v>
@@ -2693,7 +2696,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -2705,7 +2708,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -2723,7 +2726,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -2735,7 +2738,7 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -2753,7 +2756,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -2765,7 +2768,7 @@
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -2783,7 +2786,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -2795,7 +2798,7 @@
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G7">
         <v>4</v>
@@ -2813,7 +2816,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -2825,7 +2828,7 @@
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -2843,7 +2846,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -2855,7 +2858,7 @@
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -2873,7 +2876,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -2885,7 +2888,7 @@
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -2903,7 +2906,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -2915,7 +2918,7 @@
         <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -2933,7 +2936,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -2945,7 +2948,7 @@
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -2963,7 +2966,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -2975,7 +2978,7 @@
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -2993,7 +2996,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -3005,7 +3008,7 @@
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -3023,7 +3026,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -3035,7 +3038,7 @@
         <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -3053,7 +3056,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C16">
         <v>2</v>
@@ -3065,7 +3068,7 @@
         <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -3083,7 +3086,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C17">
         <v>2</v>
@@ -3096,7 +3099,7 @@
         <v>37</v>
       </c>
       <c r="F17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -3196,7 +3199,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -3208,7 +3211,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -3226,7 +3229,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -3238,7 +3241,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -3256,7 +3259,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -3268,7 +3271,7 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -3286,7 +3289,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -3298,7 +3301,7 @@
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -3316,7 +3319,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -3328,7 +3331,7 @@
         <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -3346,7 +3349,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -3358,7 +3361,7 @@
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -3376,7 +3379,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -3388,7 +3391,7 @@
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -3406,7 +3409,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -3418,7 +3421,7 @@
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -3436,7 +3439,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -3448,7 +3451,7 @@
         <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -3466,7 +3469,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -3478,7 +3481,7 @@
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -3496,7 +3499,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -3508,7 +3511,7 @@
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -3526,7 +3529,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -3538,7 +3541,7 @@
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -3556,7 +3559,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -3568,7 +3571,7 @@
         <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -3586,7 +3589,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -3598,7 +3601,7 @@
         <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -3616,7 +3619,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C17">
         <v>2</v>
@@ -3628,7 +3631,7 @@
         <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -3646,7 +3649,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -3658,7 +3661,7 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -3676,7 +3679,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -3689,7 +3692,7 @@
         <v>31</v>
       </c>
       <c r="F19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G19">
         <v>5</v>

--- a/FPS_Test/Assets/Excel/ExcelData.xlsx
+++ b/FPS_Test/Assets/Excel/ExcelData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\GitHub\game_team\FPS_Test\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FF4A75-58CD-4335-90A0-DF6AFD670DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E22E2D48-7825-4E5D-BE15-E8240E9D0F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3390" yWindow="-13860" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3390" yWindow="-13860" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="common" sheetId="1" r:id="rId1"/>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F2" t="s">
         <v>15</v>
@@ -1078,7 +1078,7 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E20">
         <f>100-SUM(E2:E19)</f>
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F20" t="s">
         <v>35</v>
@@ -1752,7 +1752,7 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F2" t="s">
         <v>17</v>
@@ -1782,7 +1782,7 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="E29">
         <f>100-SUM(E2:E28)</f>
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F29" t="s">
         <v>56</v>
@@ -2582,7 +2582,7 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2645,7 +2645,7 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F2" t="s">
         <v>19</v>
@@ -2675,7 +2675,7 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F3" t="s">
         <v>20</v>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="E17">
         <f>100-SUM(E2:E16)</f>
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F17" t="s">
         <v>67</v>
@@ -3178,7 +3178,7 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F2" t="s">
         <v>21</v>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="E19">
         <f>100-SUM(E2:E18)</f>
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F19" t="s">
         <v>79</v>

--- a/FPS_Test/Assets/Excel/ExcelData.xlsx
+++ b/FPS_Test/Assets/Excel/ExcelData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\GitHub\game_team\FPS_Test\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E22E2D48-7825-4E5D-BE15-E8240E9D0F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55C5D158-6F85-4110-8A81-5A4493147363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3390" yWindow="-13860" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
   <si>
     <t>id</t>
   </si>
@@ -88,32 +88,7 @@
     <t>typeName</t>
   </si>
   <si>
-    <t>1×1</t>
-  </si>
-  <si>
-    <t>1×1_body</t>
-  </si>
-  <si>
-    <t>1×1_gauntlet</t>
-  </si>
-  <si>
-    <t>1×1_head</t>
-  </si>
-  <si>
-    <t>1×1_shoes</t>
-  </si>
-  <si>
-    <t>1×1_Weapon</t>
-  </si>
-  <si>
-    <t>1×2</t>
-  </si>
-  <si>
     <t>price</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>1×1_head</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -992,7 +967,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I102"/>
+  <dimension ref="A1:I100"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4.625" customWidth="1"/>
@@ -1031,7 +1006,7 @@
         <v>14</v>
       </c>
       <c r="I1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1039,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1048,20 +1023,20 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H2" t="str">
-        <f>IF(G2=0,"Helmet",IF(G2=1,"Armor",IF(G2=2,"Gauntlet",IF(G2=3,"Shoes",IF(G2=4,"Weapon","None")))))</f>
-        <v>None</v>
+        <f t="shared" ref="H2:H5" si="0">IF(G2=0,"Helmet",IF(G2=1,"Armor",IF(G2=2,"Gauntlet",IF(G2=3,"Shoes",IF(G2=4,"Weapon","None")))))</f>
+        <v>Weapon</v>
       </c>
       <c r="I2">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1069,29 +1044,29 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H3" t="str">
-        <f>IF(G3=0,"Helmet",IF(G3=1,"Armor",IF(G3=2,"Gauntlet",IF(G3=3,"Shoes",IF(G3=4,"Weapon","None")))))</f>
-        <v>Armor</v>
+        <f t="shared" si="0"/>
+        <v>Weapon</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1099,49 +1074,49 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G4">
         <v>4</v>
       </c>
       <c r="H4" t="str">
-        <f t="shared" ref="H4:H7" si="0">IF(G4=0,"Helmet",IF(G4=1,"Armor",IF(G4=2,"Gauntlet",IF(G4=3,"Shoes",IF(G4=4,"Weapon","None")))))</f>
+        <f t="shared" si="0"/>
         <v>Weapon</v>
       </c>
       <c r="I4">
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -1154,42 +1129,42 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>83</v>
+        <v>16</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" t="str">
-        <f t="shared" si="0"/>
-        <v>Weapon</v>
+        <f t="shared" ref="H6:H17" si="1">IF(G6=0,"Helmet",IF(G6=1,"Armor",IF(G6=2,"Gauntlet",IF(G6=3,"Shoes",IF(G6=4,"Weapon","None")))))</f>
+        <v>None</v>
       </c>
       <c r="I6">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1198,28 +1173,28 @@
         <v>2</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7" t="str">
-        <f t="shared" si="0"/>
-        <v>Weapon</v>
+        <f t="shared" si="1"/>
+        <v>None</v>
       </c>
       <c r="I7">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1228,20 +1203,20 @@
         <v>1</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G8">
         <v>5</v>
       </c>
       <c r="H8" t="str">
-        <f t="shared" ref="H8:H19" si="1">IF(G8=0,"Helmet",IF(G8=1,"Armor",IF(G8=2,"Gauntlet",IF(G8=3,"Shoes",IF(G8=4,"Weapon","None")))))</f>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1249,19 +1224,19 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -1271,7 +1246,7 @@
         <v>None</v>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1279,7 +1254,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1288,10 +1263,10 @@
         <v>1</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -1301,7 +1276,7 @@
         <v>None</v>
       </c>
       <c r="I10">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1309,7 +1284,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1318,10 +1293,10 @@
         <v>1</v>
       </c>
       <c r="E11">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -1331,7 +1306,7 @@
         <v>None</v>
       </c>
       <c r="I11">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1339,19 +1314,19 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -1361,7 +1336,7 @@
         <v>None</v>
       </c>
       <c r="I12">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1369,7 +1344,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1378,10 +1353,10 @@
         <v>1</v>
       </c>
       <c r="E13">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -1391,7 +1366,7 @@
         <v>None</v>
       </c>
       <c r="I13">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1399,19 +1374,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -1421,7 +1396,7 @@
         <v>None</v>
       </c>
       <c r="I14">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1429,7 +1404,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1438,10 +1413,10 @@
         <v>1</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -1451,7 +1426,7 @@
         <v>None</v>
       </c>
       <c r="I15">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1459,7 +1434,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -1468,10 +1443,10 @@
         <v>1</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -1481,7 +1456,7 @@
         <v>None</v>
       </c>
       <c r="I16">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1489,7 +1464,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -1498,10 +1473,10 @@
         <v>1</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -1511,7 +1486,7 @@
         <v>None</v>
       </c>
       <c r="I17">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1519,92 +1494,34 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <f>100-SUM(E2:E17)</f>
+        <v>14</v>
       </c>
       <c r="F18" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G18">
         <v>5</v>
       </c>
       <c r="H18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(G18=0,"Helmet",IF(G18=1,"Armor",IF(G18=2,"Gauntlet",IF(G18=3,"Shoes",IF(G18=4,"Weapon","None")))))</f>
         <v>None</v>
       </c>
       <c r="I18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19">
-        <v>17</v>
-      </c>
-      <c r="B19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19">
-        <v>1</v>
-      </c>
-      <c r="F19" t="s">
-        <v>34</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-      <c r="H19" t="str">
-        <f t="shared" si="1"/>
-        <v>None</v>
-      </c>
-      <c r="I19">
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>2</v>
-      </c>
-      <c r="E20">
-        <f>100-SUM(E2:E19)</f>
-        <v>14</v>
-      </c>
-      <c r="F20" t="s">
-        <v>35</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-      <c r="H20" t="str">
-        <f>IF(G20=0,"Helmet",IF(G20=1,"Armor",IF(G20=2,"Gauntlet",IF(G20=3,"Shoes",IF(G20=4,"Weapon","None")))))</f>
-        <v>None</v>
-      </c>
-      <c r="I20">
-        <v>50</v>
-      </c>
-    </row>
+    <row r="19" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="20" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="21" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="23" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -1685,8 +1602,6 @@
     <row r="98" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="99" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="100" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="101" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="102" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -1696,7 +1611,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
@@ -1735,7 +1650,7 @@
         <v>14</v>
       </c>
       <c r="I1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.4">
@@ -1743,7 +1658,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1752,20 +1667,20 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H2" t="str">
-        <f>IF(G2=0,"Helmet",IF(G2=1,"Armor",IF(G2=2,"Gauntlet",IF(G2=3,"Shoes",IF(G2=4,"Weapon","None")))))</f>
-        <v>Gauntlet</v>
+        <f t="shared" ref="H2:H5" si="0">IF(G2=0,"Helmet",IF(G2=1,"Armor",IF(G2=2,"Gauntlet",IF(G2=3,"Shoes",IF(G2=4,"Weapon","None")))))</f>
+        <v>Weapon</v>
       </c>
       <c r="I2">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
@@ -1773,29 +1688,29 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H3" t="str">
-        <f>IF(G3=0,"Helmet",IF(G3=1,"Armor",IF(G3=2,"Gauntlet",IF(G3=3,"Shoes",IF(G3=4,"Weapon","None")))))</f>
-        <v>Helmet</v>
+        <f t="shared" si="0"/>
+        <v>Weapon</v>
       </c>
       <c r="I3">
-        <v>80</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
@@ -1803,25 +1718,25 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G4">
         <v>4</v>
       </c>
       <c r="H4" t="str">
-        <f t="shared" ref="H4:H7" si="0">IF(G4=0,"Helmet",IF(G4=1,"Armor",IF(G4=2,"Gauntlet",IF(G4=3,"Shoes",IF(G4=4,"Weapon","None")))))</f>
+        <f t="shared" si="0"/>
         <v>Weapon</v>
       </c>
       <c r="I4">
@@ -1833,19 +1748,19 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -1863,29 +1778,29 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" t="str">
-        <f t="shared" si="0"/>
-        <v>Weapon</v>
+        <f t="shared" ref="H6:H27" si="1">IF(G6=0,"Helmet",IF(G6=1,"Armor",IF(G6=2,"Gauntlet",IF(G6=3,"Shoes",IF(G6=4,"Weapon","None")))))</f>
+        <v>None</v>
       </c>
       <c r="I6">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.4">
@@ -1893,29 +1808,29 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7" t="str">
-        <f t="shared" si="0"/>
-        <v>Weapon</v>
+        <f t="shared" si="1"/>
+        <v>None</v>
       </c>
       <c r="I7">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.4">
@@ -1923,7 +1838,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1935,13 +1850,13 @@
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G8">
         <v>5</v>
       </c>
       <c r="H8" t="str">
-        <f t="shared" ref="H8:H29" si="1">IF(G8=0,"Helmet",IF(G8=1,"Armor",IF(G8=2,"Gauntlet",IF(G8=3,"Shoes",IF(G8=4,"Weapon","None")))))</f>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I8">
@@ -1953,7 +1868,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1965,7 +1880,7 @@
         <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -1983,7 +1898,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1995,7 +1910,7 @@
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -2005,7 +1920,7 @@
         <v>None</v>
       </c>
       <c r="I10">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
@@ -2013,7 +1928,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -2025,7 +1940,7 @@
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -2035,7 +1950,7 @@
         <v>None</v>
       </c>
       <c r="I11">
-        <v>150</v>
+        <v>230</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.4">
@@ -2043,7 +1958,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -2055,7 +1970,7 @@
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -2073,7 +1988,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -2085,7 +2000,7 @@
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -2103,7 +2018,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -2115,7 +2030,7 @@
         <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -2125,7 +2040,7 @@
         <v>None</v>
       </c>
       <c r="I14">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
@@ -2133,7 +2048,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -2145,17 +2060,17 @@
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G15">
         <v>5</v>
       </c>
       <c r="H15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(G15=0,"Helmet",IF(G15=1,"Armor",IF(G15=2,"Gauntlet",IF(G15=3,"Shoes",IF(G15=4,"Weapon","None")))))</f>
         <v>None</v>
       </c>
       <c r="I15">
-        <v>230</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.4">
@@ -2163,7 +2078,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -2175,17 +2090,17 @@
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G16">
         <v>5</v>
       </c>
       <c r="H16" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(G16=0,"Helmet",IF(G16=1,"Armor",IF(G16=2,"Gauntlet",IF(G16=3,"Shoes",IF(G16=4,"Weapon","None")))))</f>
         <v>None</v>
       </c>
       <c r="I16">
-        <v>150</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.4">
@@ -2193,7 +2108,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -2205,17 +2120,17 @@
         <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G17">
         <v>5</v>
       </c>
       <c r="H17" t="str">
-        <f>IF(G17=0,"Helmet",IF(G17=1,"Armor",IF(G17=2,"Gauntlet",IF(G17=3,"Shoes",IF(G17=4,"Weapon","None")))))</f>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I17">
-        <v>200</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
@@ -2223,7 +2138,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -2235,13 +2150,13 @@
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="G18">
         <v>5</v>
       </c>
       <c r="H18" t="str">
-        <f>IF(G18=0,"Helmet",IF(G18=1,"Armor",IF(G18=2,"Gauntlet",IF(G18=3,"Shoes",IF(G18=4,"Weapon","None")))))</f>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I18">
@@ -2253,7 +2168,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -2265,7 +2180,7 @@
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -2275,7 +2190,7 @@
         <v>None</v>
       </c>
       <c r="I19">
-        <v>170</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.4">
@@ -2283,7 +2198,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -2295,7 +2210,7 @@
         <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -2305,7 +2220,7 @@
         <v>None</v>
       </c>
       <c r="I20">
-        <v>170</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.4">
@@ -2313,7 +2228,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -2325,7 +2240,7 @@
         <v>3</v>
       </c>
       <c r="F21" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -2335,7 +2250,7 @@
         <v>None</v>
       </c>
       <c r="I21">
-        <v>130</v>
+        <v>220</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.4">
@@ -2343,7 +2258,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -2355,7 +2270,7 @@
         <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -2365,7 +2280,7 @@
         <v>None</v>
       </c>
       <c r="I22">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.4">
@@ -2373,7 +2288,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -2385,7 +2300,7 @@
         <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G23">
         <v>5</v>
@@ -2395,7 +2310,7 @@
         <v>None</v>
       </c>
       <c r="I23">
-        <v>220</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.4">
@@ -2403,7 +2318,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -2415,7 +2330,7 @@
         <v>3</v>
       </c>
       <c r="F24" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G24">
         <v>5</v>
@@ -2425,7 +2340,7 @@
         <v>None</v>
       </c>
       <c r="I24">
-        <v>150</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.4">
@@ -2433,7 +2348,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -2445,7 +2360,7 @@
         <v>3</v>
       </c>
       <c r="F25" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G25">
         <v>5</v>
@@ -2463,7 +2378,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -2475,7 +2390,7 @@
         <v>3</v>
       </c>
       <c r="F26" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="G26">
         <v>5</v>
@@ -2485,7 +2400,7 @@
         <v>None</v>
       </c>
       <c r="I26">
-        <v>180</v>
+        <v>170</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.4">
@@ -2493,7 +2408,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -2502,10 +2417,11 @@
         <v>1</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <f>100-SUM(E2:E26)</f>
+        <v>29</v>
       </c>
       <c r="F27" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -2515,67 +2431,6 @@
         <v>None</v>
       </c>
       <c r="I27">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A28">
-        <v>26</v>
-      </c>
-      <c r="B28" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-      <c r="E28">
-        <v>3</v>
-      </c>
-      <c r="F28" t="s">
-        <v>55</v>
-      </c>
-      <c r="G28">
-        <v>5</v>
-      </c>
-      <c r="H28" t="str">
-        <f t="shared" si="1"/>
-        <v>None</v>
-      </c>
-      <c r="I28">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A29">
-        <v>27</v>
-      </c>
-      <c r="B29" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-      <c r="D29">
-        <v>1</v>
-      </c>
-      <c r="E29">
-        <f>100-SUM(E2:E28)</f>
-        <v>29</v>
-      </c>
-      <c r="F29" t="s">
-        <v>56</v>
-      </c>
-      <c r="G29">
-        <v>5</v>
-      </c>
-      <c r="H29" t="str">
-        <f t="shared" si="1"/>
-        <v>None</v>
-      </c>
-      <c r="I29">
         <v>300</v>
       </c>
     </row>
@@ -2588,7 +2443,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
@@ -2628,7 +2483,7 @@
         <v>14</v>
       </c>
       <c r="I1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.4">
@@ -2636,7 +2491,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -2645,20 +2500,20 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2" t="str">
-        <f>IF(G2=0,"Helmet",IF(G2=1,"Armor",IF(G2=2,"Gauntlet",IF(G2=3,"Shoes",IF(G2=4,"Weapon","None")))))</f>
-        <v>Shoes</v>
+        <f t="shared" ref="H2:H5" si="0">IF(G2=0,"Helmet",IF(G2=1,"Armor",IF(G2=2,"Gauntlet",IF(G2=3,"Shoes",IF(G2=4,"Weapon","None")))))</f>
+        <v>Weapon</v>
       </c>
       <c r="I2">
-        <v>300</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
@@ -2666,25 +2521,25 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="G3">
         <v>4</v>
       </c>
       <c r="H3" t="str">
-        <f>IF(G3=0,"Helmet",IF(G3=1,"Armor",IF(G3=2,"Gauntlet",IF(G3=3,"Shoes",IF(G3=4,"Weapon","None")))))</f>
+        <f t="shared" si="0"/>
         <v>Weapon</v>
       </c>
       <c r="I3">
@@ -2696,25 +2551,25 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="G4">
         <v>4</v>
       </c>
       <c r="H4" t="str">
-        <f t="shared" ref="H4:H7" si="0">IF(G4=0,"Helmet",IF(G4=1,"Armor",IF(G4=2,"Gauntlet",IF(G4=3,"Shoes",IF(G4=4,"Weapon","None")))))</f>
+        <f t="shared" si="0"/>
         <v>Weapon</v>
       </c>
       <c r="I4">
@@ -2726,19 +2581,19 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -2756,26 +2611,26 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" t="str">
-        <f t="shared" si="0"/>
-        <v>Weapon</v>
+        <f t="shared" ref="H6:H15" si="1">IF(G6=0,"Helmet",IF(G6=1,"Armor",IF(G6=2,"Gauntlet",IF(G6=3,"Shoes",IF(G6=4,"Weapon","None")))))</f>
+        <v>None</v>
       </c>
       <c r="I6">
         <v>500</v>
@@ -2786,29 +2641,29 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7" t="str">
-        <f t="shared" si="0"/>
-        <v>Weapon</v>
+        <f t="shared" si="1"/>
+        <v>None</v>
       </c>
       <c r="I7">
-        <v>500</v>
+        <v>800</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.4">
@@ -2816,10 +2671,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -2828,17 +2683,17 @@
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G8">
         <v>5</v>
       </c>
       <c r="H8" t="str">
-        <f t="shared" ref="H8:H17" si="1">IF(G8=0,"Helmet",IF(G8=1,"Armor",IF(G8=2,"Gauntlet",IF(G8=3,"Shoes",IF(G8=4,"Weapon","None")))))</f>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I8">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.4">
@@ -2846,7 +2701,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -2858,7 +2713,7 @@
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -2868,7 +2723,7 @@
         <v>None</v>
       </c>
       <c r="I9">
-        <v>800</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.4">
@@ -2876,10 +2731,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -2888,7 +2743,7 @@
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -2898,7 +2753,7 @@
         <v>None</v>
       </c>
       <c r="I10">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
@@ -2906,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -2918,7 +2773,7 @@
         <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -2928,7 +2783,7 @@
         <v>None</v>
       </c>
       <c r="I11">
-        <v>1700</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.4">
@@ -2936,10 +2791,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -2948,7 +2803,7 @@
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -2958,7 +2813,7 @@
         <v>None</v>
       </c>
       <c r="I12">
-        <v>620</v>
+        <v>800</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.4">
@@ -2966,19 +2821,19 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13">
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -2988,7 +2843,7 @@
         <v>None</v>
       </c>
       <c r="I13">
-        <v>1500</v>
+        <v>800</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.4">
@@ -2996,19 +2851,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14">
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -3018,7 +2873,7 @@
         <v>None</v>
       </c>
       <c r="I14">
-        <v>800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
@@ -3026,19 +2881,20 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <f>100-SUM(E2:E14)</f>
+        <v>47</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -3048,67 +2904,6 @@
         <v>None</v>
       </c>
       <c r="I15">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A16">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
-      <c r="E16">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>66</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-      <c r="H16" t="str">
-        <f t="shared" si="1"/>
-        <v>None</v>
-      </c>
-      <c r="I16">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A17">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17">
-        <v>2</v>
-      </c>
-      <c r="D17">
-        <v>2</v>
-      </c>
-      <c r="E17">
-        <f>100-SUM(E2:E16)</f>
-        <v>47</v>
-      </c>
-      <c r="F17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-      <c r="H17" t="str">
-        <f t="shared" si="1"/>
-        <v>None</v>
-      </c>
-      <c r="I17">
         <v>3000</v>
       </c>
     </row>
@@ -3121,7 +2916,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
@@ -3161,7 +2956,7 @@
         <v>14</v>
       </c>
       <c r="I1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.4">
@@ -3169,29 +2964,29 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H2" t="str">
-        <f>IF(G2=0,"Helmet",IF(G2=1,"Armor",IF(G2=2,"Gauntlet",IF(G2=3,"Shoes",IF(G2=4,"Weapon","None")))))</f>
-        <v>None</v>
+        <f t="shared" ref="H2:H5" si="0">IF(G2=0,"Helmet",IF(G2=1,"Armor",IF(G2=2,"Gauntlet",IF(G2=3,"Shoes",IF(G2=4,"Weapon","None")))))</f>
+        <v>Weapon</v>
       </c>
       <c r="I2">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
@@ -3199,25 +2994,25 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="G3">
         <v>4</v>
       </c>
       <c r="H3" t="str">
-        <f t="shared" ref="H3:H6" si="0">IF(G3=0,"Helmet",IF(G3=1,"Armor",IF(G3=2,"Gauntlet",IF(G3=3,"Shoes",IF(G3=4,"Weapon","None")))))</f>
+        <f t="shared" si="0"/>
         <v>Weapon</v>
       </c>
       <c r="I3">
@@ -3229,19 +3024,19 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -3259,7 +3054,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -3271,7 +3066,7 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -3289,29 +3084,29 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" t="str">
-        <f t="shared" si="0"/>
-        <v>Weapon</v>
+        <f t="shared" ref="H6:H18" si="1">IF(G6=0,"Helmet",IF(G6=1,"Armor",IF(G6=2,"Gauntlet",IF(G6=3,"Shoes",IF(G6=4,"Weapon","None")))))</f>
+        <v>None</v>
       </c>
       <c r="I6">
-        <v>500</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.4">
@@ -3319,29 +3114,29 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G7">
         <v>5</v>
       </c>
       <c r="H7" t="str">
-        <f t="shared" ref="H7:H19" si="1">IF(G7=0,"Helmet",IF(G7=1,"Armor",IF(G7=2,"Gauntlet",IF(G7=3,"Shoes",IF(G7=4,"Weapon","None")))))</f>
+        <f t="shared" si="1"/>
         <v>None</v>
       </c>
       <c r="I7">
-        <v>3400</v>
+        <v>830</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.4">
@@ -3349,7 +3144,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -3361,7 +3156,7 @@
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -3371,7 +3166,7 @@
         <v>None</v>
       </c>
       <c r="I8">
-        <v>830</v>
+        <v>900</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.4">
@@ -3379,19 +3174,19 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9">
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -3401,7 +3196,7 @@
         <v>None</v>
       </c>
       <c r="I9">
-        <v>900</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.4">
@@ -3409,19 +3204,19 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -3431,7 +3226,7 @@
         <v>None</v>
       </c>
       <c r="I10">
-        <v>3500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
@@ -3439,19 +3234,19 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11">
         <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -3461,7 +3256,7 @@
         <v>None</v>
       </c>
       <c r="I11">
-        <v>1100</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.4">
@@ -3469,19 +3264,19 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12">
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -3491,7 +3286,7 @@
         <v>None</v>
       </c>
       <c r="I12">
-        <v>2700</v>
+        <v>810</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.4">
@@ -3499,7 +3294,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -3511,7 +3306,7 @@
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -3521,7 +3316,7 @@
         <v>None</v>
       </c>
       <c r="I13">
-        <v>810</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.4">
@@ -3529,19 +3324,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14">
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -3551,7 +3346,7 @@
         <v>None</v>
       </c>
       <c r="I14">
-        <v>1500</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
@@ -3559,19 +3354,19 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15">
         <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -3581,7 +3376,7 @@
         <v>None</v>
       </c>
       <c r="I15">
-        <v>3300</v>
+        <v>800</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.4">
@@ -3589,10 +3384,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -3601,7 +3396,7 @@
         <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -3611,7 +3406,7 @@
         <v>None</v>
       </c>
       <c r="I16">
-        <v>800</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.4">
@@ -3619,19 +3414,19 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C17">
         <v>2</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -3641,7 +3436,7 @@
         <v>None</v>
       </c>
       <c r="I17">
-        <v>1700</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
@@ -3649,19 +3444,20 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18">
         <v>3</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <f>100-SUM(E2:E17)</f>
+        <v>36</v>
       </c>
       <c r="F18" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -3671,37 +3467,6 @@
         <v>None</v>
       </c>
       <c r="I18">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A19">
-        <v>17</v>
-      </c>
-      <c r="B19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>3</v>
-      </c>
-      <c r="E19">
-        <f>100-SUM(E2:E18)</f>
-        <v>36</v>
-      </c>
-      <c r="F19" t="s">
-        <v>79</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-      <c r="H19" t="str">
-        <f t="shared" si="1"/>
-        <v>None</v>
-      </c>
-      <c r="I19">
         <v>4000</v>
       </c>
     </row>

--- a/FPS_Test/Assets/Excel/ExcelData.xlsx
+++ b/FPS_Test/Assets/Excel/ExcelData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\GitHub\game_team\FPS_Test\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55C5D158-6F85-4110-8A81-5A4493147363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D373BA7-3860-4A7F-A49F-2132507F02D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3390" yWindow="-13860" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3390" yWindow="-13860" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="common" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="98">
   <si>
     <t>id</t>
   </si>
@@ -599,6 +599,39 @@
     </rPh>
     <rPh sb="8" eb="9">
       <t>サカズキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Head</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Body</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Shoes</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>頭装備</t>
+    <rPh sb="0" eb="3">
+      <t>アタマソウビ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>体装備</t>
+    <rPh sb="0" eb="3">
+      <t>カラダソウビ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>靴装備</t>
+    <rPh sb="0" eb="3">
+      <t>クツソウビ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1611,7 +1644,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
@@ -1658,7 +1691,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1670,14 +1703,14 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H2" t="str">
-        <f t="shared" ref="H2:H5" si="0">IF(G2=0,"Helmet",IF(G2=1,"Armor",IF(G2=2,"Gauntlet",IF(G2=3,"Shoes",IF(G2=4,"Weapon","None")))))</f>
-        <v>Weapon</v>
+        <f t="shared" ref="H2:H4" si="0">IF(G2=0,"Helmet",IF(G2=1,"Armor",IF(G2=2,"Gauntlet",IF(G2=3,"Shoes",IF(G2=4,"Weapon","None")))))</f>
+        <v>Helmet</v>
       </c>
       <c r="I2">
         <v>200</v>
@@ -1688,26 +1721,26 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H3" t="str">
         <f t="shared" si="0"/>
-        <v>Weapon</v>
+        <v>Armor</v>
       </c>
       <c r="I3">
         <v>200</v>
@@ -1718,26 +1751,26 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4" t="str">
         <f t="shared" si="0"/>
-        <v>Weapon</v>
+        <v>Shoes</v>
       </c>
       <c r="I4">
         <v>200</v>
@@ -1748,25 +1781,25 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G5">
         <v>4</v>
       </c>
       <c r="H5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="H5:H8" si="1">IF(G5=0,"Helmet",IF(G5=1,"Armor",IF(G5=2,"Gauntlet",IF(G5=3,"Shoes",IF(G5=4,"Weapon","None")))))</f>
         <v>Weapon</v>
       </c>
       <c r="I5">
@@ -1778,29 +1811,29 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6" t="str">
-        <f t="shared" ref="H6:H27" si="1">IF(G6=0,"Helmet",IF(G6=1,"Armor",IF(G6=2,"Gauntlet",IF(G6=3,"Shoes",IF(G6=4,"Weapon","None")))))</f>
-        <v>None</v>
+        <f t="shared" si="1"/>
+        <v>Weapon</v>
       </c>
       <c r="I6">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.4">
@@ -1808,29 +1841,29 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="1"/>
-        <v>None</v>
+        <v>Weapon</v>
       </c>
       <c r="I7">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.4">
@@ -1838,29 +1871,29 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H8" t="str">
         <f t="shared" si="1"/>
-        <v>None</v>
+        <v>Weapon</v>
       </c>
       <c r="I8">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.4">
@@ -1868,7 +1901,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1877,16 +1910,16 @@
         <v>1</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G9">
         <v>5</v>
       </c>
       <c r="H9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="H9:H30" si="2">IF(G9=0,"Helmet",IF(G9=1,"Armor",IF(G9=2,"Gauntlet",IF(G9=3,"Shoes",IF(G9=4,"Weapon","None")))))</f>
         <v>None</v>
       </c>
       <c r="I9">
@@ -1898,7 +1931,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1907,20 +1940,20 @@
         <v>1</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G10">
         <v>5</v>
       </c>
       <c r="H10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>None</v>
       </c>
       <c r="I10">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
@@ -1928,7 +1961,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1937,20 +1970,20 @@
         <v>1</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G11">
         <v>5</v>
       </c>
       <c r="H11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>None</v>
       </c>
       <c r="I11">
-        <v>230</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.4">
@@ -1958,7 +1991,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1967,20 +2000,20 @@
         <v>1</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G12">
         <v>5</v>
       </c>
       <c r="H12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>None</v>
       </c>
       <c r="I12">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.4">
@@ -1988,7 +2021,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1997,20 +2030,20 @@
         <v>1</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G13">
         <v>5</v>
       </c>
       <c r="H13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>None</v>
       </c>
       <c r="I13">
-        <v>230</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.4">
@@ -2018,7 +2051,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -2027,20 +2060,20 @@
         <v>1</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G14">
         <v>5</v>
       </c>
       <c r="H14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>None</v>
       </c>
       <c r="I14">
-        <v>150</v>
+        <v>230</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
@@ -2048,7 +2081,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -2057,16 +2090,16 @@
         <v>1</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G15">
         <v>5</v>
       </c>
       <c r="H15" t="str">
-        <f>IF(G15=0,"Helmet",IF(G15=1,"Armor",IF(G15=2,"Gauntlet",IF(G15=3,"Shoes",IF(G15=4,"Weapon","None")))))</f>
+        <f t="shared" si="2"/>
         <v>None</v>
       </c>
       <c r="I15">
@@ -2078,7 +2111,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -2087,20 +2120,20 @@
         <v>1</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G16">
         <v>5</v>
       </c>
       <c r="H16" t="str">
-        <f>IF(G16=0,"Helmet",IF(G16=1,"Armor",IF(G16=2,"Gauntlet",IF(G16=3,"Shoes",IF(G16=4,"Weapon","None")))))</f>
+        <f t="shared" si="2"/>
         <v>None</v>
       </c>
       <c r="I16">
-        <v>170</v>
+        <v>230</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.4">
@@ -2108,7 +2141,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -2117,20 +2150,20 @@
         <v>1</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G17">
         <v>5</v>
       </c>
       <c r="H17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>None</v>
       </c>
       <c r="I17">
-        <v>170</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
@@ -2138,7 +2171,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -2147,20 +2180,20 @@
         <v>1</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G18">
         <v>5</v>
       </c>
       <c r="H18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(G18=0,"Helmet",IF(G18=1,"Armor",IF(G18=2,"Gauntlet",IF(G18=3,"Shoes",IF(G18=4,"Weapon","None")))))</f>
         <v>None</v>
       </c>
       <c r="I18">
-        <v>170</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.4">
@@ -2168,7 +2201,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -2177,20 +2210,20 @@
         <v>1</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F19" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G19">
         <v>5</v>
       </c>
       <c r="H19" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(G19=0,"Helmet",IF(G19=1,"Armor",IF(G19=2,"Gauntlet",IF(G19=3,"Shoes",IF(G19=4,"Weapon","None")))))</f>
         <v>None</v>
       </c>
       <c r="I19">
-        <v>130</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.4">
@@ -2198,7 +2231,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -2207,20 +2240,20 @@
         <v>1</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F20" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G20">
         <v>5</v>
       </c>
       <c r="H20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>None</v>
       </c>
       <c r="I20">
-        <v>120</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.4">
@@ -2228,7 +2261,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -2237,20 +2270,20 @@
         <v>1</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F21" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G21">
         <v>5</v>
       </c>
       <c r="H21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>None</v>
       </c>
       <c r="I21">
-        <v>220</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.4">
@@ -2258,7 +2291,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -2267,20 +2300,20 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G22">
         <v>5</v>
       </c>
       <c r="H22" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>None</v>
       </c>
       <c r="I22">
-        <v>150</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.4">
@@ -2288,7 +2321,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -2297,20 +2330,20 @@
         <v>1</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G23">
         <v>5</v>
       </c>
       <c r="H23" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>None</v>
       </c>
       <c r="I23">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.4">
@@ -2318,7 +2351,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -2327,20 +2360,20 @@
         <v>1</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G24">
         <v>5</v>
       </c>
       <c r="H24" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>None</v>
       </c>
       <c r="I24">
-        <v>180</v>
+        <v>220</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.4">
@@ -2348,7 +2381,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -2357,16 +2390,16 @@
         <v>1</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G25">
         <v>5</v>
       </c>
       <c r="H25" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>None</v>
       </c>
       <c r="I25">
@@ -2378,7 +2411,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -2387,20 +2420,20 @@
         <v>1</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G26">
         <v>5</v>
       </c>
       <c r="H26" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>None</v>
       </c>
       <c r="I26">
-        <v>170</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.4">
@@ -2408,29 +2441,119 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="F27" t="s">
+        <v>45</v>
+      </c>
+      <c r="G27">
+        <v>5</v>
+      </c>
+      <c r="H27" t="str">
+        <f t="shared" si="2"/>
+        <v>None</v>
+      </c>
+      <c r="I27">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="F28" t="s">
+        <v>46</v>
+      </c>
+      <c r="G28">
+        <v>5</v>
+      </c>
+      <c r="H28" t="str">
+        <f t="shared" si="2"/>
+        <v>None</v>
+      </c>
+      <c r="I28">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="F29" t="s">
+        <v>47</v>
+      </c>
+      <c r="G29">
+        <v>5</v>
+      </c>
+      <c r="H29" t="str">
+        <f t="shared" si="2"/>
+        <v>None</v>
+      </c>
+      <c r="I29">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
         <v>48</v>
       </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-      <c r="E27">
-        <f>100-SUM(E2:E26)</f>
-        <v>29</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <f>100-SUM(E2:E29)</f>
+        <v>44</v>
+      </c>
+      <c r="F30" t="s">
         <v>48</v>
       </c>
-      <c r="G27">
-        <v>5</v>
-      </c>
-      <c r="H27" t="str">
-        <f t="shared" si="1"/>
-        <v>None</v>
-      </c>
-      <c r="I27">
+      <c r="G30">
+        <v>5</v>
+      </c>
+      <c r="H30" t="str">
+        <f t="shared" si="2"/>
+        <v>None</v>
+      </c>
+      <c r="I30">
         <v>300</v>
       </c>
     </row>

--- a/FPS_Test/Assets/Excel/ExcelData.xlsx
+++ b/FPS_Test/Assets/Excel/ExcelData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\GitHub\game_team\FPS_Test\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D373BA7-3860-4A7F-A49F-2132507F02D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F38713A1-58EA-4845-932E-8BBF714A86F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3390" yWindow="-13860" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3390" yWindow="-13860" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="common" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="102">
   <si>
     <t>id</t>
   </si>
@@ -603,18 +603,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Head</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Body</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Shoes</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>頭装備</t>
     <rPh sb="0" eb="3">
       <t>アタマソウビ</t>
@@ -633,6 +621,34 @@
     <rPh sb="0" eb="3">
       <t>クツソウビ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>RareHead</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>RareBody</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>RareShoes</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Rare短剣</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>UniqueHead</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>UniqueBody</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>UniqueShoes</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1691,19 +1707,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
         <v>92</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2" t="s">
-        <v>95</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1721,19 +1737,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
         <v>93</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3" t="s">
-        <v>96</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -1751,19 +1767,19 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4" t="s">
         <v>94</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4" t="s">
-        <v>97</v>
       </c>
       <c r="G4">
         <v>3</v>
@@ -1781,7 +1797,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -2566,7 +2582,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
@@ -2614,7 +2630,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -2626,17 +2642,17 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H2" t="str">
-        <f t="shared" ref="H2:H5" si="0">IF(G2=0,"Helmet",IF(G2=1,"Armor",IF(G2=2,"Gauntlet",IF(G2=3,"Shoes",IF(G2=4,"Weapon","None")))))</f>
-        <v>Weapon</v>
+        <f t="shared" ref="H2:H4" si="0">IF(G2=0,"Helmet",IF(G2=1,"Armor",IF(G2=2,"Gauntlet",IF(G2=3,"Shoes",IF(G2=4,"Weapon","None")))))</f>
+        <v>Helmet</v>
       </c>
       <c r="I2">
-        <v>500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
@@ -2644,29 +2660,29 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H3" t="str">
         <f t="shared" si="0"/>
-        <v>Weapon</v>
+        <v>Armor</v>
       </c>
       <c r="I3">
-        <v>500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
@@ -2674,29 +2690,29 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4" t="str">
         <f t="shared" si="0"/>
-        <v>Weapon</v>
+        <v>Shoes</v>
       </c>
       <c r="I4">
-        <v>500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.4">
@@ -2704,25 +2720,25 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G5">
         <v>4</v>
       </c>
       <c r="H5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="H5:H8" si="1">IF(G5=0,"Helmet",IF(G5=1,"Armor",IF(G5=2,"Gauntlet",IF(G5=3,"Shoes",IF(G5=4,"Weapon","None")))))</f>
         <v>Weapon</v>
       </c>
       <c r="I5">
@@ -2734,26 +2750,26 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6" t="str">
-        <f t="shared" ref="H6:H15" si="1">IF(G6=0,"Helmet",IF(G6=1,"Armor",IF(G6=2,"Gauntlet",IF(G6=3,"Shoes",IF(G6=4,"Weapon","None")))))</f>
-        <v>None</v>
+        <f t="shared" si="1"/>
+        <v>Weapon</v>
       </c>
       <c r="I6">
         <v>500</v>
@@ -2764,29 +2780,29 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="1"/>
-        <v>None</v>
+        <v>Weapon</v>
       </c>
       <c r="I7">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.4">
@@ -2794,29 +2810,29 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H8" t="str">
         <f t="shared" si="1"/>
-        <v>None</v>
+        <v>Weapon</v>
       </c>
       <c r="I8">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.4">
@@ -2824,29 +2840,29 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9">
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G9">
         <v>5</v>
       </c>
       <c r="H9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="H9:H18" si="2">IF(G9=0,"Helmet",IF(G9=1,"Armor",IF(G9=2,"Gauntlet",IF(G9=3,"Shoes",IF(G9=4,"Weapon","None")))))</f>
         <v>None</v>
       </c>
       <c r="I9">
-        <v>1700</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.4">
@@ -2854,29 +2870,29 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G10">
         <v>5</v>
       </c>
       <c r="H10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>None</v>
       </c>
       <c r="I10">
-        <v>620</v>
+        <v>800</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
@@ -2884,29 +2900,29 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G11">
         <v>5</v>
       </c>
       <c r="H11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>None</v>
       </c>
       <c r="I11">
-        <v>1500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.4">
@@ -2914,29 +2930,29 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12">
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G12">
         <v>5</v>
       </c>
       <c r="H12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>None</v>
       </c>
       <c r="I12">
-        <v>800</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.4">
@@ -2944,7 +2960,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -2956,17 +2972,17 @@
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G13">
         <v>5</v>
       </c>
       <c r="H13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>None</v>
       </c>
       <c r="I13">
-        <v>800</v>
+        <v>620</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.4">
@@ -2974,7 +2990,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -2986,17 +3002,17 @@
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G14">
         <v>5</v>
       </c>
       <c r="H14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>None</v>
       </c>
       <c r="I14">
-        <v>1200</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
@@ -3004,29 +3020,119 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>5</v>
+      </c>
+      <c r="F15" t="s">
+        <v>56</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15" t="str">
+        <f t="shared" si="2"/>
+        <v>None</v>
+      </c>
+      <c r="I15">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>5</v>
+      </c>
+      <c r="F16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+      <c r="H16" t="str">
+        <f t="shared" si="2"/>
+        <v>None</v>
+      </c>
+      <c r="I16">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17">
+        <v>5</v>
+      </c>
+      <c r="F17" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+      <c r="H17" t="str">
+        <f t="shared" si="2"/>
+        <v>None</v>
+      </c>
+      <c r="I17">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
         <v>59</v>
       </c>
-      <c r="C15">
-        <v>2</v>
-      </c>
-      <c r="D15">
-        <v>2</v>
-      </c>
-      <c r="E15">
-        <f>100-SUM(E2:E14)</f>
-        <v>47</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
+      <c r="E18">
+        <f>100-SUM(E2:E17)</f>
+        <v>41</v>
+      </c>
+      <c r="F18" t="s">
         <v>59</v>
       </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-      <c r="H15" t="str">
-        <f t="shared" si="1"/>
-        <v>None</v>
-      </c>
-      <c r="I15">
+      <c r="G18">
+        <v>5</v>
+      </c>
+      <c r="H18" t="str">
+        <f t="shared" si="2"/>
+        <v>None</v>
+      </c>
+      <c r="I18">
         <v>3000</v>
       </c>
     </row>
@@ -3039,7 +3145,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
@@ -3087,7 +3193,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -3099,17 +3205,17 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H2" t="str">
-        <f t="shared" ref="H2:H5" si="0">IF(G2=0,"Helmet",IF(G2=1,"Armor",IF(G2=2,"Gauntlet",IF(G2=3,"Shoes",IF(G2=4,"Weapon","None")))))</f>
-        <v>Weapon</v>
+        <f t="shared" ref="H2:H4" si="0">IF(G2=0,"Helmet",IF(G2=1,"Armor",IF(G2=2,"Gauntlet",IF(G2=3,"Shoes",IF(G2=4,"Weapon","None")))))</f>
+        <v>Helmet</v>
       </c>
       <c r="I2">
-        <v>500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
@@ -3117,29 +3223,29 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H3" t="str">
         <f t="shared" si="0"/>
-        <v>Weapon</v>
+        <v>Armor</v>
       </c>
       <c r="I3">
-        <v>500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
@@ -3147,29 +3253,29 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4" t="str">
         <f t="shared" si="0"/>
-        <v>Weapon</v>
+        <v>Shoes</v>
       </c>
       <c r="I4">
-        <v>500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.4">
@@ -3177,25 +3283,25 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G5">
         <v>4</v>
       </c>
       <c r="H5" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(G5=0,"Helmet",IF(G5=1,"Armor",IF(G5=2,"Gauntlet",IF(G5=3,"Shoes",IF(G5=4,"Weapon","None")))))</f>
         <v>Weapon</v>
       </c>
       <c r="I5">
@@ -3207,29 +3313,29 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6" t="str">
-        <f t="shared" ref="H6:H18" si="1">IF(G6=0,"Helmet",IF(G6=1,"Armor",IF(G6=2,"Gauntlet",IF(G6=3,"Shoes",IF(G6=4,"Weapon","None")))))</f>
-        <v>None</v>
+        <f t="shared" ref="H6:H8" si="1">IF(G6=0,"Helmet",IF(G6=1,"Armor",IF(G6=2,"Gauntlet",IF(G6=3,"Shoes",IF(G6=4,"Weapon","None")))))</f>
+        <v>Weapon</v>
       </c>
       <c r="I6">
-        <v>3400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.4">
@@ -3237,29 +3343,29 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="1"/>
-        <v>None</v>
+        <v>Weapon</v>
       </c>
       <c r="I7">
-        <v>830</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.4">
@@ -3267,29 +3373,29 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H8" t="str">
         <f t="shared" si="1"/>
-        <v>None</v>
+        <v>Weapon</v>
       </c>
       <c r="I8">
-        <v>900</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.4">
@@ -3297,7 +3403,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -3309,17 +3415,17 @@
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G9">
         <v>5</v>
       </c>
       <c r="H9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="H9:H21" si="2">IF(G9=0,"Helmet",IF(G9=1,"Armor",IF(G9=2,"Gauntlet",IF(G9=3,"Shoes",IF(G9=4,"Weapon","None")))))</f>
         <v>None</v>
       </c>
       <c r="I9">
-        <v>3500</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.4">
@@ -3327,7 +3433,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -3339,17 +3445,17 @@
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G10">
         <v>5</v>
       </c>
       <c r="H10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>None</v>
       </c>
       <c r="I10">
-        <v>1100</v>
+        <v>830</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
@@ -3357,29 +3463,29 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G11">
         <v>5</v>
       </c>
       <c r="H11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>None</v>
       </c>
       <c r="I11">
-        <v>2700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.4">
@@ -3387,29 +3493,29 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12">
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G12">
         <v>5</v>
       </c>
       <c r="H12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>None</v>
       </c>
       <c r="I12">
-        <v>810</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.4">
@@ -3417,7 +3523,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -3429,17 +3535,17 @@
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G13">
         <v>5</v>
       </c>
       <c r="H13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>None</v>
       </c>
       <c r="I13">
-        <v>1500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.4">
@@ -3447,29 +3553,29 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14">
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G14">
         <v>5</v>
       </c>
       <c r="H14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>None</v>
       </c>
       <c r="I14">
-        <v>3300</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
@@ -3477,7 +3583,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -3489,17 +3595,17 @@
         <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="G15">
         <v>5</v>
       </c>
       <c r="H15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>None</v>
       </c>
       <c r="I15">
-        <v>800</v>
+        <v>810</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.4">
@@ -3507,10 +3613,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -3519,17 +3625,17 @@
         <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G16">
         <v>5</v>
       </c>
       <c r="H16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>None</v>
       </c>
       <c r="I16">
-        <v>1700</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.4">
@@ -3537,29 +3643,29 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C17">
         <v>2</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G17">
         <v>5</v>
       </c>
       <c r="H17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>None</v>
       </c>
       <c r="I17">
-        <v>10000</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
@@ -3567,29 +3673,119 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>5</v>
+      </c>
+      <c r="F18" t="s">
+        <v>72</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+      <c r="H18" t="str">
+        <f t="shared" si="2"/>
+        <v>None</v>
+      </c>
+      <c r="I18">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>5</v>
+      </c>
+      <c r="F19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+      <c r="H19" t="str">
+        <f t="shared" si="2"/>
+        <v>None</v>
+      </c>
+      <c r="I19">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+      <c r="H20" t="str">
+        <f t="shared" si="2"/>
+        <v>None</v>
+      </c>
+      <c r="I20">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
         <v>71</v>
       </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
         <v>3</v>
       </c>
-      <c r="E18">
-        <f>100-SUM(E2:E17)</f>
-        <v>36</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="E21">
+        <f>100-SUM(E2:E20)</f>
+        <v>30</v>
+      </c>
+      <c r="F21" t="s">
         <v>71</v>
       </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-      <c r="H18" t="str">
-        <f t="shared" si="1"/>
-        <v>None</v>
-      </c>
-      <c r="I18">
+      <c r="G21">
+        <v>5</v>
+      </c>
+      <c r="H21" t="str">
+        <f t="shared" si="2"/>
+        <v>None</v>
+      </c>
+      <c r="I21">
         <v>4000</v>
       </c>
     </row>

--- a/FPS_Test/Assets/Excel/ExcelData.xlsx
+++ b/FPS_Test/Assets/Excel/ExcelData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\GitHub\game_team\FPS_Test\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F38713A1-58EA-4845-932E-8BBF714A86F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E27EF2C-F7CC-4D85-8C58-47EE77790BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3390" yWindow="-13860" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6540" yWindow="-12960" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="common" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="100">
   <si>
     <t>id</t>
   </si>
@@ -473,110 +473,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Common短剣</t>
-    <rPh sb="6" eb="8">
-      <t>タンケン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Common大剣</t>
-    <rPh sb="6" eb="8">
-      <t>タイケン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Commonメイス</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Common杖</t>
-    <rPh sb="6" eb="7">
-      <t>ツエ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Common短剣</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Rare短剣</t>
-    <rPh sb="4" eb="6">
-      <t>タンケン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Rare大剣</t>
-    <rPh sb="4" eb="6">
-      <t>タイケン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Rareメイス</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Rare杖</t>
-    <rPh sb="4" eb="5">
-      <t>ツエ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Unique短剣</t>
-    <rPh sb="6" eb="8">
-      <t>タンケン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Unique大剣</t>
-    <rPh sb="6" eb="8">
-      <t>タイケン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Uniqueメイス</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Unique杖</t>
-    <rPh sb="6" eb="7">
-      <t>ツエ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Legendary短剣</t>
-    <rPh sb="9" eb="11">
-      <t>タンケン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Legendary大剣</t>
-    <rPh sb="9" eb="11">
-      <t>タイケン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Legendaryメイス</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Legendary杖</t>
-    <rPh sb="9" eb="10">
-      <t>ツエ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>小麦袋</t>
     <rPh sb="0" eb="2">
       <t>コムギ</t>
@@ -636,10 +532,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Rare短剣</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>UniqueHead</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -649,6 +541,70 @@
   </si>
   <si>
     <t>UniqueShoes</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>CommonDagger</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>CommonSword</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>CommonMace</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>CommonWand</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>RareDagger</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>RareSword</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>RareMace</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>RareWand</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>UniqueDagger</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>UniqueSword</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>UniqueMace</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>UniqueWand</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>LegendaryDagger</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>LegendarySword</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>LegendaryMace</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>LegendaryWand</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1063,7 +1019,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1075,7 +1031,7 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -1093,7 +1049,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1105,7 +1061,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -1123,7 +1079,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1135,7 +1091,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1153,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1165,7 +1121,7 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -1183,7 +1139,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1423,7 +1379,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1435,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="F14" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -1707,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1719,7 +1675,7 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1737,7 +1693,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1749,7 +1705,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -1767,7 +1723,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1779,7 +1735,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="G4">
         <v>3</v>
@@ -1797,7 +1753,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1809,7 +1765,7 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -1827,7 +1783,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1839,7 +1795,7 @@
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -1857,7 +1813,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1869,7 +1825,7 @@
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G7">
         <v>4</v>
@@ -1887,7 +1843,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1899,7 +1855,7 @@
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G8">
         <v>4</v>
@@ -2630,7 +2586,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -2642,7 +2598,7 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -2660,7 +2616,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -2672,7 +2628,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -2690,7 +2646,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -2702,7 +2658,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="G4">
         <v>3</v>
@@ -2720,7 +2676,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -2732,7 +2688,7 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -2750,7 +2706,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -2762,7 +2718,7 @@
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -2780,7 +2736,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -2792,7 +2748,7 @@
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="G7">
         <v>4</v>
@@ -2810,7 +2766,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -2822,7 +2778,7 @@
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="G8">
         <v>4</v>
@@ -3193,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -3205,7 +3161,7 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -3223,7 +3179,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -3235,7 +3191,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -3253,7 +3209,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -3265,7 +3221,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="G4">
         <v>3</v>
@@ -3283,7 +3239,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -3295,7 +3251,7 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -3313,7 +3269,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -3325,7 +3281,7 @@
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -3343,7 +3299,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -3355,7 +3311,7 @@
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G7">
         <v>4</v>
@@ -3364,7 +3320,7 @@
         <f t="shared" si="1"/>
         <v>Weapon</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>500</v>
       </c>
     </row>
@@ -3373,7 +3329,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -3385,7 +3341,7 @@
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G8">
         <v>4</v>

--- a/FPS_Test/Assets/Excel/ExcelData.xlsx
+++ b/FPS_Test/Assets/Excel/ExcelData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\GitHub\game_team\FPS_Test\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E27EF2C-F7CC-4D85-8C58-47EE77790BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F88B489F-73CD-4A6D-8EB7-78BC6055C005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6540" yWindow="-12960" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="common" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="119">
   <si>
     <t>id</t>
   </si>
@@ -605,6 +605,97 @@
   </si>
   <si>
     <t>LegendaryWand</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>LegendaryShoes</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>LegendaryGauntlet</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>LegendaryBody</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>LegendaryHead</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>UniqueGauntlet</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>腕装備</t>
+    <rPh sb="0" eb="1">
+      <t>ウデ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>ソウビ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>RareGauntlet</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HealPotion</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ヒールポーション</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>短剣</t>
+    <rPh sb="0" eb="2">
+      <t>タンケン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>大剣</t>
+    <rPh sb="0" eb="2">
+      <t>タイケン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>メイス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>杖</t>
+    <rPh sb="0" eb="1">
+      <t>ツエ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>HighPotion</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ハイポーション</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>MegaPotion</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ManaPotion</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>メガポーション</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>マナポーション</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -972,7 +1063,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I100"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4.625" customWidth="1"/>
@@ -1031,13 +1122,13 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="G2">
         <v>4</v>
       </c>
       <c r="H2" t="str">
-        <f t="shared" ref="H2:H5" si="0">IF(G2=0,"Helmet",IF(G2=1,"Armor",IF(G2=2,"Gauntlet",IF(G2=3,"Shoes",IF(G2=4,"Weapon","None")))))</f>
+        <f>IF(G2=0,"Helmet",IF(G2=1,"Armor",IF(G2=2,"Gauntlet",IF(G2=3,"Shoes",IF(G2=4,"Weapon",IF(G2=5, "None", "Potion"))))))</f>
         <v>Weapon</v>
       </c>
       <c r="I2">
@@ -1061,13 +1152,13 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="G3">
         <v>4</v>
       </c>
       <c r="H3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="H3:H18" si="0">IF(G3=0,"Helmet",IF(G3=1,"Armor",IF(G3=2,"Gauntlet",IF(G3=3,"Shoes",IF(G3=4,"Weapon",IF(G3=5, "None", "Potion"))))))</f>
         <v>Weapon</v>
       </c>
       <c r="I3">
@@ -1091,7 +1182,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1121,7 +1212,7 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -1139,59 +1230,59 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6" t="s">
+        <v>108</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+      <c r="H6" t="str">
+        <f t="shared" si="0"/>
+        <v>Potion</v>
+      </c>
+      <c r="I6">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
         <v>73</v>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
         <v>20</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F7" t="s">
         <v>16</v>
       </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6" t="str">
-        <f t="shared" ref="H6:H17" si="1">IF(G6=0,"Helmet",IF(G6=1,"Armor",IF(G6=2,"Gauntlet",IF(G6=3,"Shoes",IF(G6=4,"Weapon","None")))))</f>
-        <v>None</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>17</v>
-      </c>
       <c r="G7">
         <v>5</v>
       </c>
       <c r="H7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>None</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1199,29 +1290,29 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I8">
         <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-      <c r="H8" t="str">
-        <f t="shared" si="1"/>
-        <v>None</v>
-      </c>
-      <c r="I8">
-        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1229,7 +1320,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1238,20 +1329,20 @@
         <v>1</v>
       </c>
       <c r="E9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G9">
         <v>5</v>
       </c>
       <c r="H9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>None</v>
       </c>
       <c r="I9">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1259,7 +1350,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1271,17 +1362,17 @@
         <v>8</v>
       </c>
       <c r="F10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="H10" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I10">
         <v>20</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-      <c r="H10" t="str">
-        <f t="shared" si="1"/>
-        <v>None</v>
-      </c>
-      <c r="I10">
-        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1289,7 +1380,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1298,20 +1389,20 @@
         <v>1</v>
       </c>
       <c r="E11">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G11">
         <v>5</v>
       </c>
       <c r="H11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>None</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1319,29 +1410,29 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G12">
         <v>5</v>
       </c>
       <c r="H12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>None</v>
       </c>
       <c r="I12">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1349,29 +1440,29 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G13">
         <v>5</v>
       </c>
       <c r="H13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>None</v>
       </c>
       <c r="I13">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1379,7 +1470,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1388,20 +1479,20 @@
         <v>1</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="G14">
         <v>5</v>
       </c>
       <c r="H14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>None</v>
       </c>
       <c r="I14">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1409,7 +1500,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1421,17 +1512,17 @@
         <v>2</v>
       </c>
       <c r="F15" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="G15">
         <v>5</v>
       </c>
       <c r="H15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>None</v>
       </c>
       <c r="I15">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1439,7 +1530,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -1448,20 +1539,20 @@
         <v>1</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G16">
         <v>5</v>
       </c>
       <c r="H16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>None</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1469,7 +1560,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -1481,17 +1572,17 @@
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G17">
         <v>5</v>
       </c>
       <c r="H17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>None</v>
       </c>
       <c r="I17">
-        <v>50</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1499,33 +1590,62 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <f>100-SUM(E2:E17)</f>
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G18">
         <v>5</v>
       </c>
       <c r="H18" t="str">
-        <f>IF(G18=0,"Helmet",IF(G18=1,"Armor",IF(G18=2,"Gauntlet",IF(G18=3,"Shoes",IF(G18=4,"Weapon","None")))))</f>
+        <f t="shared" si="0"/>
         <v>None</v>
       </c>
       <c r="I18">
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="19" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19">
+        <f>100-SUM(E2:E18)</f>
+        <v>12</v>
+      </c>
+      <c r="F19" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+      <c r="H19" t="str">
+        <f>IF(G19=0,"Helmet",IF(G19=1,"Armor",IF(G19=2,"Gauntlet",IF(G19=3,"Shoes",IF(G19=4,"Weapon",IF(G19=5, "None", "Potion"))))))</f>
+        <v>None</v>
+      </c>
+      <c r="I19">
+        <v>50</v>
+      </c>
+    </row>
     <row r="20" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="21" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -1607,6 +1727,7 @@
     <row r="98" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="99" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="100" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="101" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -1616,7 +1737,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
@@ -1624,7 +1745,7 @@
     <col min="3" max="4" width="8.625" customWidth="1"/>
     <col min="5" max="5" width="10.375" customWidth="1"/>
     <col min="6" max="6" width="19.625" customWidth="1"/>
-    <col min="7" max="7" width="10.125" customWidth="1"/>
+    <col min="7" max="7" width="15.875" customWidth="1"/>
     <col min="8" max="8" width="12.75" customWidth="1"/>
     <col min="9" max="1025" width="8.625" customWidth="1"/>
   </cols>
@@ -1681,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="str">
-        <f t="shared" ref="H2:H4" si="0">IF(G2=0,"Helmet",IF(G2=1,"Armor",IF(G2=2,"Gauntlet",IF(G2=3,"Shoes",IF(G2=4,"Weapon","None")))))</f>
+        <f>IF(G2=0,"Helmet",IF(G2=1,"Armor",IF(G2=2,"Gauntlet",IF(G2=3,"Shoes",IF(G2=4,"Weapon",IF(G2=5, "None", "Potion"))))))</f>
         <v>Helmet</v>
       </c>
       <c r="I2">
@@ -1711,7 +1832,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="H3:H33" si="0">IF(G3=0,"Helmet",IF(G3=1,"Armor",IF(G3=2,"Gauntlet",IF(G3=3,"Shoes",IF(G3=4,"Weapon",IF(G3=5, "None", "Potion"))))))</f>
         <v>Armor</v>
       </c>
       <c r="I3">
@@ -1723,7 +1844,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1735,14 +1856,14 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4" t="str">
         <f t="shared" si="0"/>
-        <v>Shoes</v>
+        <v>Gauntlet</v>
       </c>
       <c r="I4">
         <v>200</v>
@@ -1753,7 +1874,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1765,14 +1886,14 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H5" t="str">
-        <f t="shared" ref="H5:H8" si="1">IF(G5=0,"Helmet",IF(G5=1,"Armor",IF(G5=2,"Gauntlet",IF(G5=3,"Shoes",IF(G5=4,"Weapon","None")))))</f>
-        <v>Weapon</v>
+        <f t="shared" si="0"/>
+        <v>Shoes</v>
       </c>
       <c r="I5">
         <v>200</v>
@@ -1783,25 +1904,25 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="G6">
         <v>4</v>
       </c>
       <c r="H6" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Weapon</v>
       </c>
       <c r="I6">
@@ -1813,25 +1934,25 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="G7">
         <v>4</v>
       </c>
       <c r="H7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Weapon</v>
       </c>
       <c r="I7">
@@ -1843,7 +1964,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1855,13 +1976,13 @@
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="G8">
         <v>4</v>
       </c>
       <c r="H8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Weapon</v>
       </c>
       <c r="I8">
@@ -1873,29 +1994,29 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9">
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H9" t="str">
-        <f t="shared" ref="H9:H30" si="2">IF(G9=0,"Helmet",IF(G9=1,"Armor",IF(G9=2,"Gauntlet",IF(G9=3,"Shoes",IF(G9=4,"Weapon","None")))))</f>
-        <v>None</v>
+        <f t="shared" si="0"/>
+        <v>Weapon</v>
       </c>
       <c r="I9">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.4">
@@ -1903,7 +2024,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1915,17 +2036,17 @@
         <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>29</v>
+        <v>114</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H10" t="str">
-        <f t="shared" si="2"/>
-        <v>None</v>
+        <f t="shared" si="0"/>
+        <v>Potion</v>
       </c>
       <c r="I10">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
@@ -1933,7 +2054,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1942,20 +2063,20 @@
         <v>1</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>30</v>
+        <v>117</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H11" t="str">
-        <f t="shared" si="2"/>
-        <v>None</v>
+        <f t="shared" si="0"/>
+        <v>Potion</v>
       </c>
       <c r="I11">
-        <v>150</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.4">
@@ -1963,7 +2084,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1975,17 +2096,17 @@
         <v>2</v>
       </c>
       <c r="F12" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H12" t="str">
-        <f t="shared" si="2"/>
-        <v>None</v>
+        <f t="shared" si="0"/>
+        <v>Potion</v>
       </c>
       <c r="I12">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.4">
@@ -1993,7 +2114,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -2005,17 +2126,17 @@
         <v>2</v>
       </c>
       <c r="F13" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G13">
         <v>5</v>
       </c>
       <c r="H13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>None</v>
       </c>
       <c r="I13">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.4">
@@ -2023,7 +2144,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -2035,17 +2156,17 @@
         <v>2</v>
       </c>
       <c r="F14" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G14">
         <v>5</v>
       </c>
       <c r="H14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>None</v>
       </c>
       <c r="I14">
-        <v>230</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
@@ -2053,7 +2174,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -2065,17 +2186,17 @@
         <v>2</v>
       </c>
       <c r="F15" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G15">
         <v>5</v>
       </c>
       <c r="H15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>None</v>
       </c>
       <c r="I15">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.4">
@@ -2083,7 +2204,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -2095,17 +2216,17 @@
         <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G16">
         <v>5</v>
       </c>
       <c r="H16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>None</v>
       </c>
       <c r="I16">
-        <v>230</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.4">
@@ -2113,7 +2234,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -2125,17 +2246,17 @@
         <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G17">
         <v>5</v>
       </c>
       <c r="H17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>None</v>
       </c>
       <c r="I17">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
@@ -2143,7 +2264,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -2155,17 +2276,17 @@
         <v>2</v>
       </c>
       <c r="F18" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G18">
         <v>5</v>
       </c>
       <c r="H18" t="str">
-        <f>IF(G18=0,"Helmet",IF(G18=1,"Armor",IF(G18=2,"Gauntlet",IF(G18=3,"Shoes",IF(G18=4,"Weapon","None")))))</f>
+        <f t="shared" si="0"/>
         <v>None</v>
       </c>
       <c r="I18">
-        <v>200</v>
+        <v>230</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.4">
@@ -2173,7 +2294,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -2185,17 +2306,17 @@
         <v>2</v>
       </c>
       <c r="F19" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="G19">
         <v>5</v>
       </c>
       <c r="H19" t="str">
-        <f>IF(G19=0,"Helmet",IF(G19=1,"Armor",IF(G19=2,"Gauntlet",IF(G19=3,"Shoes",IF(G19=4,"Weapon","None")))))</f>
+        <f t="shared" si="0"/>
         <v>None</v>
       </c>
       <c r="I19">
-        <v>170</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.4">
@@ -2203,7 +2324,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -2215,17 +2336,17 @@
         <v>2</v>
       </c>
       <c r="F20" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G20">
         <v>5</v>
       </c>
       <c r="H20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>None</v>
       </c>
       <c r="I20">
-        <v>170</v>
+        <v>230</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.4">
@@ -2233,7 +2354,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -2245,17 +2366,17 @@
         <v>2</v>
       </c>
       <c r="F21" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G21">
         <v>5</v>
       </c>
       <c r="H21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>None</v>
       </c>
       <c r="I21">
-        <v>170</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.4">
@@ -2263,7 +2384,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -2275,17 +2396,17 @@
         <v>2</v>
       </c>
       <c r="F22" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G22">
         <v>5</v>
       </c>
       <c r="H22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>None</v>
       </c>
       <c r="I22">
-        <v>130</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.4">
@@ -2293,7 +2414,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -2305,17 +2426,17 @@
         <v>2</v>
       </c>
       <c r="F23" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G23">
         <v>5</v>
       </c>
       <c r="H23" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>None</v>
       </c>
       <c r="I23">
-        <v>120</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.4">
@@ -2323,7 +2444,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -2335,17 +2456,17 @@
         <v>2</v>
       </c>
       <c r="F24" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G24">
         <v>5</v>
       </c>
       <c r="H24" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>None</v>
       </c>
       <c r="I24">
-        <v>220</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.4">
@@ -2353,7 +2474,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -2365,17 +2486,17 @@
         <v>2</v>
       </c>
       <c r="F25" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G25">
         <v>5</v>
       </c>
       <c r="H25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>None</v>
       </c>
       <c r="I25">
-        <v>150</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.4">
@@ -2383,7 +2504,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -2395,17 +2516,17 @@
         <v>2</v>
       </c>
       <c r="F26" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G26">
         <v>5</v>
       </c>
       <c r="H26" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>None</v>
       </c>
       <c r="I26">
-        <v>150</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.4">
@@ -2413,7 +2534,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -2425,17 +2546,17 @@
         <v>2</v>
       </c>
       <c r="F27" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G27">
         <v>5</v>
       </c>
       <c r="H27" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>None</v>
       </c>
       <c r="I27">
-        <v>180</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.4">
@@ -2443,7 +2564,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -2455,17 +2576,17 @@
         <v>2</v>
       </c>
       <c r="F28" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G28">
         <v>5</v>
       </c>
       <c r="H28" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>None</v>
       </c>
       <c r="I28">
-        <v>150</v>
+        <v>220</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.4">
@@ -2473,7 +2594,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -2485,17 +2606,17 @@
         <v>2</v>
       </c>
       <c r="F29" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G29">
         <v>5</v>
       </c>
       <c r="H29" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>None</v>
       </c>
       <c r="I29">
-        <v>170</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.4">
@@ -2503,29 +2624,149 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>2</v>
+      </c>
+      <c r="F30" t="s">
+        <v>44</v>
+      </c>
+      <c r="G30">
+        <v>5</v>
+      </c>
+      <c r="H30" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I30">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>2</v>
+      </c>
+      <c r="F31" t="s">
+        <v>45</v>
+      </c>
+      <c r="G31">
+        <v>5</v>
+      </c>
+      <c r="H31" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I31">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>2</v>
+      </c>
+      <c r="F32" t="s">
+        <v>46</v>
+      </c>
+      <c r="G32">
+        <v>5</v>
+      </c>
+      <c r="H32" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I32">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>2</v>
+      </c>
+      <c r="F33" t="s">
+        <v>47</v>
+      </c>
+      <c r="G33">
+        <v>5</v>
+      </c>
+      <c r="H33" t="str">
+        <f t="shared" si="0"/>
+        <v>None</v>
+      </c>
+      <c r="I33">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
         <v>48</v>
       </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
-      <c r="E30">
-        <f>100-SUM(E2:E29)</f>
-        <v>44</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <f>100-SUM(E2:E33)</f>
+        <v>37</v>
+      </c>
+      <c r="F34" t="s">
         <v>48</v>
       </c>
-      <c r="G30">
-        <v>5</v>
-      </c>
-      <c r="H30" t="str">
-        <f t="shared" si="2"/>
-        <v>None</v>
-      </c>
-      <c r="I30">
+      <c r="G34">
+        <v>5</v>
+      </c>
+      <c r="H34" t="str">
+        <f>IF(G34=0,"Helmet",IF(G34=1,"Armor",IF(G34=2,"Gauntlet",IF(G34=3,"Shoes",IF(G34=4,"Weapon",IF(G34=5, "None", "Potion"))))))</f>
+        <v>None</v>
+      </c>
+      <c r="I34">
         <v>300</v>
       </c>
     </row>
@@ -2538,7 +2779,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
@@ -2604,11 +2845,11 @@
         <v>0</v>
       </c>
       <c r="H2" t="str">
-        <f t="shared" ref="H2:H4" si="0">IF(G2=0,"Helmet",IF(G2=1,"Armor",IF(G2=2,"Gauntlet",IF(G2=3,"Shoes",IF(G2=4,"Weapon","None")))))</f>
+        <f t="shared" ref="H2:H5" si="0">IF(G2=0,"Helmet",IF(G2=1,"Armor",IF(G2=2,"Gauntlet",IF(G2=3,"Shoes",IF(G2=4,"Weapon","None")))))</f>
         <v>Helmet</v>
       </c>
       <c r="I2">
-        <v>200</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
@@ -2638,7 +2879,7 @@
         <v>Armor</v>
       </c>
       <c r="I3">
-        <v>200</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
@@ -2646,7 +2887,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -2658,17 +2899,17 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4" t="str">
         <f t="shared" si="0"/>
-        <v>Shoes</v>
+        <v>Gauntlet</v>
       </c>
       <c r="I4">
-        <v>200</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.4">
@@ -2676,7 +2917,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -2688,14 +2929,14 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H5" t="str">
-        <f t="shared" ref="H5:H8" si="1">IF(G5=0,"Helmet",IF(G5=1,"Armor",IF(G5=2,"Gauntlet",IF(G5=3,"Shoes",IF(G5=4,"Weapon","None")))))</f>
-        <v>Weapon</v>
+        <f t="shared" si="0"/>
+        <v>Shoes</v>
       </c>
       <c r="I5">
         <v>500</v>
@@ -2706,25 +2947,25 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G6">
         <v>4</v>
       </c>
       <c r="H6" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="H6:H9" si="1">IF(G6=0,"Helmet",IF(G6=1,"Armor",IF(G6=2,"Gauntlet",IF(G6=3,"Shoes",IF(G6=4,"Weapon","None")))))</f>
         <v>Weapon</v>
       </c>
       <c r="I6">
@@ -2736,19 +2977,19 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G7">
         <v>4</v>
@@ -2766,7 +3007,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -2778,7 +3019,7 @@
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G8">
         <v>4</v>
@@ -2796,26 +3037,26 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H9" t="str">
-        <f t="shared" ref="H9:H18" si="2">IF(G9=0,"Helmet",IF(G9=1,"Armor",IF(G9=2,"Gauntlet",IF(G9=3,"Shoes",IF(G9=4,"Weapon","None")))))</f>
-        <v>None</v>
+        <f t="shared" si="1"/>
+        <v>Weapon</v>
       </c>
       <c r="I9">
         <v>500</v>
@@ -2826,29 +3067,29 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G10">
         <v>5</v>
       </c>
       <c r="H10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="H10:H19" si="2">IF(G10=0,"Helmet",IF(G10=1,"Armor",IF(G10=2,"Gauntlet",IF(G10=3,"Shoes",IF(G10=4,"Weapon","None")))))</f>
         <v>None</v>
       </c>
       <c r="I10">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
@@ -2856,19 +3097,19 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11">
         <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -2878,7 +3119,7 @@
         <v>None</v>
       </c>
       <c r="I11">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.4">
@@ -2886,19 +3127,19 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12">
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -2908,7 +3149,7 @@
         <v>None</v>
       </c>
       <c r="I12">
-        <v>1700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.4">
@@ -2916,19 +3157,19 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13">
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -2938,7 +3179,7 @@
         <v>None</v>
       </c>
       <c r="I13">
-        <v>620</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.4">
@@ -2946,19 +3187,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -2968,7 +3209,7 @@
         <v>None</v>
       </c>
       <c r="I14">
-        <v>1500</v>
+        <v>620</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
@@ -2976,19 +3217,19 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C15">
         <v>2</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15">
         <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -2998,7 +3239,7 @@
         <v>None</v>
       </c>
       <c r="I15">
-        <v>800</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.4">
@@ -3006,10 +3247,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -3018,7 +3259,7 @@
         <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -3036,19 +3277,19 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17">
         <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -3058,7 +3299,7 @@
         <v>None</v>
       </c>
       <c r="I17">
-        <v>1200</v>
+        <v>800</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
@@ -3066,7 +3307,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -3075,11 +3316,10 @@
         <v>2</v>
       </c>
       <c r="E18">
-        <f>100-SUM(E2:E17)</f>
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -3089,6 +3329,37 @@
         <v>None</v>
       </c>
       <c r="I18">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19">
+        <f>100-SUM(E2:E18)</f>
+        <v>39</v>
+      </c>
+      <c r="F19" t="s">
+        <v>59</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+      <c r="H19" t="str">
+        <f t="shared" si="2"/>
+        <v>None</v>
+      </c>
+      <c r="I19">
         <v>3000</v>
       </c>
     </row>
@@ -3101,7 +3372,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
@@ -3149,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -3167,11 +3438,11 @@
         <v>0</v>
       </c>
       <c r="H2" t="str">
-        <f t="shared" ref="H2:H4" si="0">IF(G2=0,"Helmet",IF(G2=1,"Armor",IF(G2=2,"Gauntlet",IF(G2=3,"Shoes",IF(G2=4,"Weapon","None")))))</f>
+        <f t="shared" ref="H2:H5" si="0">IF(G2=0,"Helmet",IF(G2=1,"Armor",IF(G2=2,"Gauntlet",IF(G2=3,"Shoes",IF(G2=4,"Weapon","None")))))</f>
         <v>Helmet</v>
       </c>
       <c r="I2">
-        <v>200</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
@@ -3179,7 +3450,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -3201,7 +3472,7 @@
         <v>Armor</v>
       </c>
       <c r="I3">
-        <v>200</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
@@ -3209,7 +3480,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -3221,17 +3492,17 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4" t="str">
         <f t="shared" si="0"/>
-        <v>Shoes</v>
+        <v>Gauntlet</v>
       </c>
       <c r="I4">
-        <v>200</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.4">
@@ -3239,7 +3510,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -3251,17 +3522,17 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H5" t="str">
-        <f>IF(G5=0,"Helmet",IF(G5=1,"Armor",IF(G5=2,"Gauntlet",IF(G5=3,"Shoes",IF(G5=4,"Weapon","None")))))</f>
-        <v>Weapon</v>
+        <f t="shared" si="0"/>
+        <v>Shoes</v>
       </c>
       <c r="I5">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
@@ -3269,29 +3540,29 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G6">
         <v>4</v>
       </c>
       <c r="H6" t="str">
-        <f t="shared" ref="H6:H8" si="1">IF(G6=0,"Helmet",IF(G6=1,"Armor",IF(G6=2,"Gauntlet",IF(G6=3,"Shoes",IF(G6=4,"Weapon","None")))))</f>
+        <f>IF(G6=0,"Helmet",IF(G6=1,"Armor",IF(G6=2,"Gauntlet",IF(G6=3,"Shoes",IF(G6=4,"Weapon","None")))))</f>
         <v>Weapon</v>
       </c>
       <c r="I6">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.4">
@@ -3299,29 +3570,29 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G7">
         <v>4</v>
       </c>
       <c r="H7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="H7:H9" si="1">IF(G7=0,"Helmet",IF(G7=1,"Armor",IF(G7=2,"Gauntlet",IF(G7=3,"Shoes",IF(G7=4,"Weapon","None")))))</f>
         <v>Weapon</v>
       </c>
-      <c r="I7" s="1">
-        <v>500</v>
+      <c r="I7">
+        <v>1000</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.4">
@@ -3329,7 +3600,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -3341,7 +3612,7 @@
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G8">
         <v>4</v>
@@ -3351,7 +3622,7 @@
         <v>Weapon</v>
       </c>
       <c r="I8">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.4">
@@ -3359,29 +3630,29 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H9" t="str">
-        <f t="shared" ref="H9:H21" si="2">IF(G9=0,"Helmet",IF(G9=1,"Armor",IF(G9=2,"Gauntlet",IF(G9=3,"Shoes",IF(G9=4,"Weapon","None")))))</f>
-        <v>None</v>
+        <f t="shared" si="1"/>
+        <v>Weapon</v>
       </c>
       <c r="I9">
-        <v>3400</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.4">
@@ -3389,29 +3660,29 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G10">
         <v>5</v>
       </c>
       <c r="H10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="H10:H22" si="2">IF(G10=0,"Helmet",IF(G10=1,"Armor",IF(G10=2,"Gauntlet",IF(G10=3,"Shoes",IF(G10=4,"Weapon","None")))))</f>
         <v>None</v>
       </c>
       <c r="I10">
-        <v>830</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
@@ -3419,7 +3690,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -3431,7 +3702,7 @@
         <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -3441,7 +3712,7 @@
         <v>None</v>
       </c>
       <c r="I11">
-        <v>900</v>
+        <v>830</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.4">
@@ -3449,19 +3720,19 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12">
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -3471,7 +3742,7 @@
         <v>None</v>
       </c>
       <c r="I12">
-        <v>3500</v>
+        <v>900</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.4">
@@ -3479,19 +3750,19 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13">
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -3501,7 +3772,7 @@
         <v>None</v>
       </c>
       <c r="I13">
-        <v>1100</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.4">
@@ -3509,19 +3780,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -3531,7 +3802,7 @@
         <v>None</v>
       </c>
       <c r="I14">
-        <v>2700</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
@@ -3539,19 +3810,19 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15">
         <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -3561,7 +3832,7 @@
         <v>None</v>
       </c>
       <c r="I15">
-        <v>810</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.4">
@@ -3569,7 +3840,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -3581,7 +3852,7 @@
         <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -3591,7 +3862,7 @@
         <v>None</v>
       </c>
       <c r="I16">
-        <v>1500</v>
+        <v>810</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.4">
@@ -3599,19 +3870,19 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17">
         <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -3621,7 +3892,7 @@
         <v>None</v>
       </c>
       <c r="I17">
-        <v>3300</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
@@ -3629,19 +3900,19 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18">
         <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -3651,7 +3922,7 @@
         <v>None</v>
       </c>
       <c r="I18">
-        <v>800</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.4">
@@ -3659,10 +3930,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -3671,7 +3942,7 @@
         <v>5</v>
       </c>
       <c r="F19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -3681,7 +3952,7 @@
         <v>None</v>
       </c>
       <c r="I19">
-        <v>1700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.4">
@@ -3689,19 +3960,19 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -3711,7 +3982,7 @@
         <v>None</v>
       </c>
       <c r="I20">
-        <v>10000</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.4">
@@ -3719,20 +3990,19 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21">
         <v>3</v>
       </c>
       <c r="E21">
-        <f>100-SUM(E2:E20)</f>
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -3742,6 +4012,37 @@
         <v>None</v>
       </c>
       <c r="I21">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>3</v>
+      </c>
+      <c r="E22">
+        <f>100-SUM(E2:E21)</f>
+        <v>28</v>
+      </c>
+      <c r="F22" t="s">
+        <v>71</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+      <c r="H22" t="str">
+        <f t="shared" si="2"/>
+        <v>None</v>
+      </c>
+      <c r="I22">
         <v>4000</v>
       </c>
     </row>

--- a/FPS_Test/Assets/Excel/ExcelData.xlsx
+++ b/FPS_Test/Assets/Excel/ExcelData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\GitHub\game_team\FPS_Test\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F88B489F-73CD-4A6D-8EB7-78BC6055C005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D45DCF3-5BAA-49CF-8668-29A1C578023A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="common" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="unique" sheetId="3" r:id="rId3"/>
     <sheet name="legendary" sheetId="4" r:id="rId4"/>
     <sheet name="treasureBox" sheetId="5" r:id="rId5"/>
+    <sheet name="jobText" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="140">
   <si>
     <t>id</t>
   </si>
@@ -697,13 +698,241 @@
   <si>
     <t>マナポーション</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>jobName</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>firstPassive</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>secondPassive</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>jobType</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>戦士</t>
+    <rPh sb="0" eb="2">
+      <t>センシ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>すべてのステータスが少しだけ上昇する</t>
+    <rPh sb="10" eb="11">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>死に至る攻撃を一度だけ体力1で耐える</t>
+    <rPh sb="0" eb="1">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>イタ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>タイリョク</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>相手の攻撃で受けるダメージをカットする</t>
+    <rPh sb="0" eb="2">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>魔法使い</t>
+    <rPh sb="0" eb="3">
+      <t>マホウツカ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>攻撃をした際に状態異常(やけど)をつけることがある</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ジョウタイイジョウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>攻撃をした際に状態異常(凍傷)をつけることがある</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ジョウタイイジョウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>トウショウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>攻撃をした際に状態異常(感電)をつけることがある</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ジョウタイイジョウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カンデン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>僧侶</t>
+    <rPh sb="0" eb="2">
+      <t>ソウリョ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>徘徊するモンスターに与えるダメージが上昇する</t>
+    <rPh sb="0" eb="2">
+      <t>ハイカイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>体力が一定時間で自動回復する</t>
+    <rPh sb="0" eb="2">
+      <t>タイリョク</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>イッテイジカン</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>ジドウカイフク</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ゲーム開始時に一定量のダメージから身を守るバリアを張る</t>
+    <rPh sb="3" eb="6">
+      <t>カイシジ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>イッテイリョウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>マモ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ハ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>盗賊</t>
+    <rPh sb="0" eb="2">
+      <t>トウゾク</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>宝箱を開封するまでの時間が短くなる</t>
+    <rPh sb="0" eb="2">
+      <t>タカラバコ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カイフウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ミジカ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>移動速度が少しだけ上昇する</t>
+    <rPh sb="0" eb="4">
+      <t>イドウソクド</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Legendaryの宝箱を開けるカギを一つ所持する</t>
+    <rPh sb="10" eb="12">
+      <t>タカラバコ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ショジ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>thirdPassive</t>
+    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -723,6 +952,13 @@
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -745,10 +981,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -4242,4 +4484,104 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1708847-E130-4755-B503-98857E4A0B91}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="10.875" customWidth="1"/>
+    <col min="2" max="4" width="52.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A2" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A3" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A4" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E4" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A5" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E5" s="3">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/FPS_Test/Assets/Excel/ExcelData.xlsx
+++ b/FPS_Test/Assets/Excel/ExcelData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\GitHub\game_team\FPS_Test\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D45DCF3-5BAA-49CF-8668-29A1C578023A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7CB01D2-2093-4F08-ACCF-E981D72F3006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="common" sheetId="1" r:id="rId1"/>

--- a/FPS_Test/Assets/Excel/ExcelData.xlsx
+++ b/FPS_Test/Assets/Excel/ExcelData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\GitHub\game_team\FPS_Test\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7CB01D2-2093-4F08-ACCF-E981D72F3006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A5006DD-7076-4B0D-87D2-F3A0D8155F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="common" sheetId="1" r:id="rId1"/>
@@ -521,26 +521,10 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>RareHead</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>RareBody</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>RareShoes</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>UniqueHead</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>UniqueBody</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>UniqueShoes</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -614,14 +598,6 @@
   </si>
   <si>
     <t>LegendaryGauntlet</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>LegendaryBody</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>LegendaryHead</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -926,6 +902,30 @@
   <si>
     <t>thirdPassive</t>
     <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>UniqueArmor</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>UniqueHelmet</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>LegendaryHelmet</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>LegendaryArmor</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>RareHelmet</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>RareArmor</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -1352,7 +1352,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1364,7 +1364,7 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -1382,7 +1382,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1394,7 +1394,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -1412,7 +1412,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1424,7 +1424,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1442,7 +1442,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1454,7 +1454,7 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -1472,7 +1472,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1484,7 +1484,7 @@
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="G6">
         <v>6</v>
@@ -2026,7 +2026,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -2056,7 +2056,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -2086,7 +2086,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -2098,7 +2098,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -2116,7 +2116,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -2146,7 +2146,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -2158,7 +2158,7 @@
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -2176,7 +2176,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -2188,7 +2188,7 @@
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="G7">
         <v>4</v>
@@ -2206,7 +2206,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -2218,7 +2218,7 @@
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G8">
         <v>4</v>
@@ -2236,7 +2236,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -2248,7 +2248,7 @@
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="G9">
         <v>4</v>
@@ -2266,7 +2266,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -2278,7 +2278,7 @@
         <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="G10">
         <v>6</v>
@@ -2296,7 +2296,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -2308,7 +2308,7 @@
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G11">
         <v>6</v>
@@ -2326,7 +2326,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -2338,7 +2338,7 @@
         <v>2</v>
       </c>
       <c r="F12" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G12">
         <v>6</v>
@@ -3069,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -3099,7 +3099,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -3129,7 +3129,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -3141,7 +3141,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -3159,7 +3159,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -3189,7 +3189,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -3201,7 +3201,7 @@
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -3219,7 +3219,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -3231,7 +3231,7 @@
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G7">
         <v>4</v>
@@ -3249,7 +3249,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -3261,7 +3261,7 @@
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G8">
         <v>4</v>
@@ -3279,7 +3279,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -3291,7 +3291,7 @@
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G9">
         <v>4</v>
@@ -3608,7 +3608,7 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3662,7 +3662,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -3692,7 +3692,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -3722,7 +3722,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -3734,7 +3734,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -3752,7 +3752,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -3782,7 +3782,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -3794,7 +3794,7 @@
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -3812,7 +3812,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -3824,7 +3824,7 @@
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G7">
         <v>4</v>
@@ -3842,7 +3842,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -3854,7 +3854,7 @@
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G8">
         <v>4</v>
@@ -3872,7 +3872,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -3884,7 +3884,7 @@
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G9">
         <v>4</v>
@@ -4497,33 +4497,33 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E2" s="3">
         <v>0</v>
@@ -4531,16 +4531,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E3" s="3">
         <v>1</v>
@@ -4548,16 +4548,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="E4" s="3">
         <v>2</v>
@@ -4565,16 +4565,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E5" s="3">
         <v>3</v>

--- a/FPS_Test/Assets/Excel/ExcelData.xlsx
+++ b/FPS_Test/Assets/Excel/ExcelData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\GitHub\game_team\FPS_Test\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A5006DD-7076-4B0D-87D2-F3A0D8155F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7992CADA-1C80-443E-865E-97306D204CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5865" yWindow="-11715" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="common" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="139">
   <si>
     <t>id</t>
   </si>
@@ -84,9 +84,6 @@
   </si>
   <si>
     <t>equipmentType</t>
-  </si>
-  <si>
-    <t>typeName</t>
   </si>
   <si>
     <t>price</t>
@@ -1305,7 +1302,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4.625" customWidth="1"/>
@@ -1314,11 +1311,10 @@
     <col min="5" max="5" width="13.375" customWidth="1"/>
     <col min="6" max="6" width="17.625" customWidth="1"/>
     <col min="7" max="7" width="14.625" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="1025" width="8.625" customWidth="1"/>
+    <col min="8" max="1024" width="8.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1343,16 +1339,13 @@
       <c r="H1" t="s">
         <v>14</v>
       </c>
-      <c r="I1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1364,25 +1357,21 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G2">
         <v>4</v>
       </c>
-      <c r="H2" t="str">
-        <f>IF(G2=0,"Helmet",IF(G2=1,"Armor",IF(G2=2,"Gauntlet",IF(G2=3,"Shoes",IF(G2=4,"Weapon",IF(G2=5, "None", "Potion"))))))</f>
-        <v>Weapon</v>
-      </c>
-      <c r="I2">
+      <c r="H2">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1394,25 +1383,21 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G3">
         <v>4</v>
       </c>
-      <c r="H3" t="str">
-        <f t="shared" ref="H3:H18" si="0">IF(G3=0,"Helmet",IF(G3=1,"Armor",IF(G3=2,"Gauntlet",IF(G3=3,"Shoes",IF(G3=4,"Weapon",IF(G3=5, "None", "Potion"))))))</f>
-        <v>Weapon</v>
-      </c>
-      <c r="I3">
+      <c r="H3">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1424,25 +1409,21 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G4">
         <v>4</v>
       </c>
-      <c r="H4" t="str">
-        <f t="shared" si="0"/>
-        <v>Weapon</v>
-      </c>
-      <c r="I4">
+      <c r="H4">
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1454,55 +1435,47 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G5">
         <v>4</v>
       </c>
-      <c r="H5" t="str">
-        <f t="shared" si="0"/>
-        <v>Weapon</v>
-      </c>
-      <c r="I5">
+      <c r="H5">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6" t="s">
         <v>101</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6" t="s">
-        <v>102</v>
       </c>
       <c r="G6">
         <v>6</v>
       </c>
-      <c r="H6" t="str">
-        <f t="shared" si="0"/>
-        <v>Potion</v>
-      </c>
-      <c r="I6">
+      <c r="H6">
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1514,25 +1487,21 @@
         <v>20</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>5</v>
       </c>
-      <c r="H7" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1544,25 +1513,21 @@
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G8">
         <v>5</v>
       </c>
-      <c r="H8" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I8">
+      <c r="H8">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1574,25 +1539,21 @@
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G9">
         <v>5</v>
       </c>
-      <c r="H9" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I9">
+      <c r="H9">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1604,25 +1565,21 @@
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G10">
         <v>5</v>
       </c>
-      <c r="H10" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I10">
+      <c r="H10">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1634,25 +1591,21 @@
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G11">
         <v>5</v>
       </c>
-      <c r="H11" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I11">
+      <c r="H11">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1664,25 +1617,21 @@
         <v>15</v>
       </c>
       <c r="F12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G12">
         <v>5</v>
       </c>
-      <c r="H12" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -1694,25 +1643,21 @@
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G13">
         <v>5</v>
       </c>
-      <c r="H13" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I13">
+      <c r="H13">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1724,25 +1669,21 @@
         <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G14">
         <v>5</v>
       </c>
-      <c r="H14" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I14">
+      <c r="H14">
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1754,25 +1695,21 @@
         <v>2</v>
       </c>
       <c r="F15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G15">
         <v>5</v>
       </c>
-      <c r="H15" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I15">
+      <c r="H15">
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -1784,25 +1721,21 @@
         <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G16">
         <v>5</v>
       </c>
-      <c r="H16" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I16">
+      <c r="H16">
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -1814,25 +1747,21 @@
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G17">
         <v>5</v>
       </c>
-      <c r="H17" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1844,25 +1773,21 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G18">
         <v>5</v>
       </c>
-      <c r="H18" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I18">
+      <c r="H18">
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1875,32 +1800,28 @@
         <v>12</v>
       </c>
       <c r="F19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G19">
         <v>5</v>
       </c>
-      <c r="H19" t="str">
-        <f>IF(G19=0,"Helmet",IF(G19=1,"Armor",IF(G19=2,"Gauntlet",IF(G19=3,"Shoes",IF(G19=4,"Weapon",IF(G19=5, "None", "Potion"))))))</f>
-        <v>None</v>
-      </c>
-      <c r="I19">
+      <c r="H19">
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="21" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="22" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="23" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="24" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="25" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="26" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="27" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="28" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="29" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="30" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="31" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="32" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="20" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="21" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="22" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="23" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="24" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="25" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="26" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="27" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="28" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="29" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="30" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="31" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="32" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="33" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="34" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="35" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -1979,7 +1900,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
@@ -1988,11 +1909,10 @@
     <col min="5" max="5" width="10.375" customWidth="1"/>
     <col min="6" max="6" width="19.625" customWidth="1"/>
     <col min="7" max="7" width="15.875" customWidth="1"/>
-    <col min="8" max="8" width="12.75" customWidth="1"/>
-    <col min="9" max="1025" width="8.625" customWidth="1"/>
+    <col min="8" max="1024" width="8.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2017,16 +1937,13 @@
       <c r="H1" t="s">
         <v>14</v>
       </c>
-      <c r="I1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -2038,25 +1955,21 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
-      <c r="H2" t="str">
-        <f>IF(G2=0,"Helmet",IF(G2=1,"Armor",IF(G2=2,"Gauntlet",IF(G2=3,"Shoes",IF(G2=4,"Weapon",IF(G2=5, "None", "Potion"))))))</f>
-        <v>Helmet</v>
-      </c>
-      <c r="I2">
+      <c r="H2">
         <v>200</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -2068,25 +1981,21 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="H3" t="str">
-        <f t="shared" ref="H3:H33" si="0">IF(G3=0,"Helmet",IF(G3=1,"Armor",IF(G3=2,"Gauntlet",IF(G3=3,"Shoes",IF(G3=4,"Weapon",IF(G3=5, "None", "Potion"))))))</f>
-        <v>Armor</v>
-      </c>
-      <c r="I3">
+      <c r="H3">
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -2098,25 +2007,21 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G4">
         <v>2</v>
       </c>
-      <c r="H4" t="str">
-        <f t="shared" si="0"/>
-        <v>Gauntlet</v>
-      </c>
-      <c r="I4">
+      <c r="H4">
         <v>200</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -2128,25 +2033,21 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G5">
         <v>3</v>
       </c>
-      <c r="H5" t="str">
-        <f t="shared" si="0"/>
-        <v>Shoes</v>
-      </c>
-      <c r="I5">
+      <c r="H5">
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -2158,25 +2059,21 @@
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G6">
         <v>4</v>
       </c>
-      <c r="H6" t="str">
-        <f t="shared" si="0"/>
-        <v>Weapon</v>
-      </c>
-      <c r="I6">
+      <c r="H6">
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -2188,25 +2085,21 @@
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G7">
         <v>4</v>
       </c>
-      <c r="H7" t="str">
-        <f t="shared" si="0"/>
-        <v>Weapon</v>
-      </c>
-      <c r="I7">
+      <c r="H7">
         <v>200</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -2218,25 +2111,21 @@
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G8">
         <v>4</v>
       </c>
-      <c r="H8" t="str">
-        <f t="shared" si="0"/>
-        <v>Weapon</v>
-      </c>
-      <c r="I8">
+      <c r="H8">
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -2248,55 +2137,47 @@
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G9">
         <v>4</v>
       </c>
-      <c r="H9" t="str">
-        <f t="shared" si="0"/>
-        <v>Weapon</v>
-      </c>
-      <c r="I9">
+      <c r="H9">
         <v>200</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10" t="s">
         <v>107</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
-      <c r="F10" t="s">
-        <v>108</v>
       </c>
       <c r="G10">
         <v>6</v>
       </c>
-      <c r="H10" t="str">
-        <f t="shared" si="0"/>
-        <v>Potion</v>
-      </c>
-      <c r="I10">
+      <c r="H10">
         <v>200</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -2308,25 +2189,21 @@
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G11">
         <v>6</v>
       </c>
-      <c r="H11" t="str">
-        <f t="shared" si="0"/>
-        <v>Potion</v>
-      </c>
-      <c r="I11">
+      <c r="H11">
         <v>300</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -2338,25 +2215,21 @@
         <v>2</v>
       </c>
       <c r="F12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G12">
         <v>6</v>
       </c>
-      <c r="H12" t="str">
-        <f t="shared" si="0"/>
-        <v>Potion</v>
-      </c>
-      <c r="I12">
+      <c r="H12">
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -2368,25 +2241,21 @@
         <v>2</v>
       </c>
       <c r="F13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G13">
         <v>5</v>
       </c>
-      <c r="H13" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I13">
+      <c r="H13">
         <v>150</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -2398,25 +2267,21 @@
         <v>2</v>
       </c>
       <c r="F14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G14">
         <v>5</v>
       </c>
-      <c r="H14" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I14">
+      <c r="H14">
         <v>150</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -2428,25 +2293,21 @@
         <v>2</v>
       </c>
       <c r="F15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G15">
         <v>5</v>
       </c>
-      <c r="H15" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I15">
+      <c r="H15">
         <v>150</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -2458,25 +2319,21 @@
         <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G16">
         <v>5</v>
       </c>
-      <c r="H16" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I16">
+      <c r="H16">
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -2488,25 +2345,21 @@
         <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G17">
         <v>5</v>
       </c>
-      <c r="H17" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I17">
+      <c r="H17">
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -2518,25 +2371,21 @@
         <v>2</v>
       </c>
       <c r="F18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G18">
         <v>5</v>
       </c>
-      <c r="H18" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I18">
+      <c r="H18">
         <v>230</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -2548,25 +2397,21 @@
         <v>2</v>
       </c>
       <c r="F19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G19">
         <v>5</v>
       </c>
-      <c r="H19" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I19">
+      <c r="H19">
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -2578,25 +2423,21 @@
         <v>2</v>
       </c>
       <c r="F20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G20">
         <v>5</v>
       </c>
-      <c r="H20" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I20">
+      <c r="H20">
         <v>230</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -2608,25 +2449,21 @@
         <v>2</v>
       </c>
       <c r="F21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G21">
         <v>5</v>
       </c>
-      <c r="H21" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I21">
+      <c r="H21">
         <v>150</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -2638,25 +2475,21 @@
         <v>2</v>
       </c>
       <c r="F22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G22">
         <v>5</v>
       </c>
-      <c r="H22" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I22">
+      <c r="H22">
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -2668,25 +2501,21 @@
         <v>2</v>
       </c>
       <c r="F23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G23">
         <v>5</v>
       </c>
-      <c r="H23" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I23">
+      <c r="H23">
         <v>170</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -2698,25 +2527,21 @@
         <v>2</v>
       </c>
       <c r="F24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G24">
         <v>5</v>
       </c>
-      <c r="H24" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I24">
+      <c r="H24">
         <v>170</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -2728,25 +2553,21 @@
         <v>2</v>
       </c>
       <c r="F25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G25">
         <v>5</v>
       </c>
-      <c r="H25" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I25">
+      <c r="H25">
         <v>170</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -2758,25 +2579,21 @@
         <v>2</v>
       </c>
       <c r="F26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G26">
         <v>5</v>
       </c>
-      <c r="H26" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I26">
+      <c r="H26">
         <v>130</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -2788,25 +2605,21 @@
         <v>2</v>
       </c>
       <c r="F27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G27">
         <v>5</v>
       </c>
-      <c r="H27" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I27">
+      <c r="H27">
         <v>120</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -2818,25 +2631,21 @@
         <v>2</v>
       </c>
       <c r="F28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G28">
         <v>5</v>
       </c>
-      <c r="H28" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I28">
+      <c r="H28">
         <v>220</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -2848,25 +2657,21 @@
         <v>2</v>
       </c>
       <c r="F29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G29">
         <v>5</v>
       </c>
-      <c r="H29" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I29">
+      <c r="H29">
         <v>150</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -2878,25 +2683,21 @@
         <v>2</v>
       </c>
       <c r="F30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G30">
         <v>5</v>
       </c>
-      <c r="H30" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I30">
+      <c r="H30">
         <v>150</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -2908,25 +2709,21 @@
         <v>2</v>
       </c>
       <c r="F31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G31">
         <v>5</v>
       </c>
-      <c r="H31" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I31">
+      <c r="H31">
         <v>180</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -2938,25 +2735,21 @@
         <v>2</v>
       </c>
       <c r="F32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G32">
         <v>5</v>
       </c>
-      <c r="H32" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I32">
+      <c r="H32">
         <v>150</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -2968,25 +2761,21 @@
         <v>2</v>
       </c>
       <c r="F33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G33">
         <v>5</v>
       </c>
-      <c r="H33" t="str">
-        <f t="shared" si="0"/>
-        <v>None</v>
-      </c>
-      <c r="I33">
+      <c r="H33">
         <v>170</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -2999,16 +2788,12 @@
         <v>37</v>
       </c>
       <c r="F34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G34">
         <v>5</v>
       </c>
-      <c r="H34" t="str">
-        <f>IF(G34=0,"Helmet",IF(G34=1,"Armor",IF(G34=2,"Gauntlet",IF(G34=3,"Shoes",IF(G34=4,"Weapon",IF(G34=5, "None", "Potion"))))))</f>
-        <v>None</v>
-      </c>
-      <c r="I34">
+      <c r="H34">
         <v>300</v>
       </c>
     </row>
@@ -3021,7 +2806,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
@@ -3030,12 +2815,11 @@
     <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="17.5" customWidth="1"/>
     <col min="7" max="7" width="15.5" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="11.5" customWidth="1"/>
-    <col min="10" max="1025" width="8.625" customWidth="1"/>
+    <col min="8" max="8" width="11.5" customWidth="1"/>
+    <col min="9" max="1024" width="8.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3060,16 +2844,13 @@
       <c r="H1" t="s">
         <v>14</v>
       </c>
-      <c r="I1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -3081,25 +2862,21 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
-      <c r="H2" t="str">
-        <f t="shared" ref="H2:H5" si="0">IF(G2=0,"Helmet",IF(G2=1,"Armor",IF(G2=2,"Gauntlet",IF(G2=3,"Shoes",IF(G2=4,"Weapon","None")))))</f>
-        <v>Helmet</v>
-      </c>
-      <c r="I2">
+      <c r="H2">
         <v>500</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -3111,55 +2888,47 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="H3" t="str">
-        <f t="shared" si="0"/>
-        <v>Armor</v>
-      </c>
-      <c r="I3">
+      <c r="H3">
         <v>500</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4" t="s">
         <v>98</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4" t="s">
-        <v>99</v>
-      </c>
       <c r="G4">
         <v>2</v>
       </c>
-      <c r="H4" t="str">
-        <f t="shared" si="0"/>
-        <v>Gauntlet</v>
-      </c>
-      <c r="I4">
+      <c r="H4">
         <v>500</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -3171,25 +2940,21 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G5">
         <v>3</v>
       </c>
-      <c r="H5" t="str">
-        <f t="shared" si="0"/>
-        <v>Shoes</v>
-      </c>
-      <c r="I5">
+      <c r="H5">
         <v>500</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -3201,25 +2966,21 @@
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G6">
         <v>4</v>
       </c>
-      <c r="H6" t="str">
-        <f t="shared" ref="H6:H9" si="1">IF(G6=0,"Helmet",IF(G6=1,"Armor",IF(G6=2,"Gauntlet",IF(G6=3,"Shoes",IF(G6=4,"Weapon","None")))))</f>
-        <v>Weapon</v>
-      </c>
-      <c r="I6">
+      <c r="H6">
         <v>500</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -3231,25 +2992,21 @@
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G7">
         <v>4</v>
       </c>
-      <c r="H7" t="str">
-        <f t="shared" si="1"/>
-        <v>Weapon</v>
-      </c>
-      <c r="I7">
+      <c r="H7">
         <v>500</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -3261,25 +3018,21 @@
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G8">
         <v>4</v>
       </c>
-      <c r="H8" t="str">
-        <f t="shared" si="1"/>
-        <v>Weapon</v>
-      </c>
-      <c r="I8">
+      <c r="H8">
         <v>500</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -3291,25 +3044,21 @@
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G9">
         <v>4</v>
       </c>
-      <c r="H9" t="str">
-        <f t="shared" si="1"/>
-        <v>Weapon</v>
-      </c>
-      <c r="I9">
+      <c r="H9">
         <v>500</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -3321,25 +3070,21 @@
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G10">
         <v>5</v>
       </c>
-      <c r="H10" t="str">
-        <f t="shared" ref="H10:H19" si="2">IF(G10=0,"Helmet",IF(G10=1,"Armor",IF(G10=2,"Gauntlet",IF(G10=3,"Shoes",IF(G10=4,"Weapon","None")))))</f>
-        <v>None</v>
-      </c>
-      <c r="I10">
+      <c r="H10">
         <v>500</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -3351,25 +3096,21 @@
         <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G11">
         <v>5</v>
       </c>
-      <c r="H11" t="str">
-        <f t="shared" si="2"/>
-        <v>None</v>
-      </c>
-      <c r="I11">
+      <c r="H11">
         <v>800</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -3381,25 +3122,21 @@
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G12">
         <v>5</v>
       </c>
-      <c r="H12" t="str">
-        <f t="shared" si="2"/>
-        <v>None</v>
-      </c>
-      <c r="I12">
+      <c r="H12">
         <v>600</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -3411,25 +3148,21 @@
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G13">
         <v>5</v>
       </c>
-      <c r="H13" t="str">
-        <f t="shared" si="2"/>
-        <v>None</v>
-      </c>
-      <c r="I13">
+      <c r="H13">
         <v>1700</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -3441,25 +3174,21 @@
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G14">
         <v>5</v>
       </c>
-      <c r="H14" t="str">
-        <f t="shared" si="2"/>
-        <v>None</v>
-      </c>
-      <c r="I14">
+      <c r="H14">
         <v>620</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -3471,25 +3200,21 @@
         <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G15">
         <v>5</v>
       </c>
-      <c r="H15" t="str">
-        <f t="shared" si="2"/>
-        <v>None</v>
-      </c>
-      <c r="I15">
+      <c r="H15">
         <v>1500</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C16">
         <v>2</v>
@@ -3501,25 +3226,21 @@
         <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G16">
         <v>5</v>
       </c>
-      <c r="H16" t="str">
-        <f t="shared" si="2"/>
-        <v>None</v>
-      </c>
-      <c r="I16">
+      <c r="H16">
         <v>800</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -3531,25 +3252,21 @@
         <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G17">
         <v>5</v>
       </c>
-      <c r="H17" t="str">
-        <f t="shared" si="2"/>
-        <v>None</v>
-      </c>
-      <c r="I17">
+      <c r="H17">
         <v>800</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -3561,25 +3278,21 @@
         <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G18">
         <v>5</v>
       </c>
-      <c r="H18" t="str">
-        <f t="shared" si="2"/>
-        <v>None</v>
-      </c>
-      <c r="I18">
+      <c r="H18">
         <v>1200</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -3592,16 +3305,12 @@
         <v>39</v>
       </c>
       <c r="F19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G19">
         <v>5</v>
       </c>
-      <c r="H19" t="str">
-        <f t="shared" si="2"/>
-        <v>None</v>
-      </c>
-      <c r="I19">
+      <c r="H19">
         <v>3000</v>
       </c>
     </row>
@@ -3614,7 +3323,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
@@ -3623,12 +3332,11 @@
     <col min="5" max="5" width="11.375" customWidth="1"/>
     <col min="6" max="6" width="20.75" customWidth="1"/>
     <col min="7" max="7" width="15.875" customWidth="1"/>
-    <col min="8" max="8" width="12.5" customWidth="1"/>
-    <col min="9" max="10" width="10.25" customWidth="1"/>
-    <col min="11" max="1025" width="8.625" customWidth="1"/>
+    <col min="8" max="9" width="10.25" customWidth="1"/>
+    <col min="10" max="1024" width="8.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3653,16 +3361,13 @@
       <c r="H1" t="s">
         <v>14</v>
       </c>
-      <c r="I1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -3674,25 +3379,21 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
-      <c r="H2" t="str">
-        <f t="shared" ref="H2:H5" si="0">IF(G2=0,"Helmet",IF(G2=1,"Armor",IF(G2=2,"Gauntlet",IF(G2=3,"Shoes",IF(G2=4,"Weapon","None")))))</f>
-        <v>Helmet</v>
-      </c>
-      <c r="I2">
+      <c r="H2">
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -3704,25 +3405,21 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="H3" t="str">
-        <f t="shared" si="0"/>
-        <v>Armor</v>
-      </c>
-      <c r="I3">
+      <c r="H3">
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -3734,25 +3431,21 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G4">
         <v>2</v>
       </c>
-      <c r="H4" t="str">
-        <f t="shared" si="0"/>
-        <v>Gauntlet</v>
-      </c>
-      <c r="I4">
+      <c r="H4">
         <v>1000</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -3764,25 +3457,21 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G5">
         <v>3</v>
       </c>
-      <c r="H5" t="str">
-        <f t="shared" si="0"/>
-        <v>Shoes</v>
-      </c>
-      <c r="I5">
+      <c r="H5">
         <v>1000</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -3794,25 +3483,21 @@
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G6">
         <v>4</v>
       </c>
-      <c r="H6" t="str">
-        <f>IF(G6=0,"Helmet",IF(G6=1,"Armor",IF(G6=2,"Gauntlet",IF(G6=3,"Shoes",IF(G6=4,"Weapon","None")))))</f>
-        <v>Weapon</v>
-      </c>
-      <c r="I6">
+      <c r="H6">
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -3824,25 +3509,21 @@
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G7">
         <v>4</v>
       </c>
-      <c r="H7" t="str">
-        <f t="shared" ref="H7:H9" si="1">IF(G7=0,"Helmet",IF(G7=1,"Armor",IF(G7=2,"Gauntlet",IF(G7=3,"Shoes",IF(G7=4,"Weapon","None")))))</f>
-        <v>Weapon</v>
-      </c>
-      <c r="I7">
+      <c r="H7">
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -3854,25 +3535,21 @@
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G8">
         <v>4</v>
       </c>
-      <c r="H8" t="str">
-        <f t="shared" si="1"/>
-        <v>Weapon</v>
-      </c>
-      <c r="I8">
+      <c r="H8">
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -3884,25 +3561,21 @@
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G9">
         <v>4</v>
       </c>
-      <c r="H9" t="str">
-        <f t="shared" si="1"/>
-        <v>Weapon</v>
-      </c>
-      <c r="I9">
+      <c r="H9">
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -3914,25 +3587,21 @@
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G10">
         <v>5</v>
       </c>
-      <c r="H10" t="str">
-        <f t="shared" ref="H10:H22" si="2">IF(G10=0,"Helmet",IF(G10=1,"Armor",IF(G10=2,"Gauntlet",IF(G10=3,"Shoes",IF(G10=4,"Weapon","None")))))</f>
-        <v>None</v>
-      </c>
-      <c r="I10">
+      <c r="H10">
         <v>3400</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -3944,25 +3613,21 @@
         <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G11">
         <v>5</v>
       </c>
-      <c r="H11" t="str">
-        <f t="shared" si="2"/>
-        <v>None</v>
-      </c>
-      <c r="I11">
+      <c r="H11">
         <v>830</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -3974,25 +3639,21 @@
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G12">
         <v>5</v>
       </c>
-      <c r="H12" t="str">
-        <f t="shared" si="2"/>
-        <v>None</v>
-      </c>
-      <c r="I12">
+      <c r="H12">
         <v>900</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -4004,25 +3665,21 @@
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G13">
         <v>5</v>
       </c>
-      <c r="H13" t="str">
-        <f t="shared" si="2"/>
-        <v>None</v>
-      </c>
-      <c r="I13">
+      <c r="H13">
         <v>3500</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -4034,25 +3691,21 @@
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G14">
         <v>5</v>
       </c>
-      <c r="H14" t="str">
-        <f t="shared" si="2"/>
-        <v>None</v>
-      </c>
-      <c r="I14">
+      <c r="H14">
         <v>1100</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -4064,25 +3717,21 @@
         <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G15">
         <v>5</v>
       </c>
-      <c r="H15" t="str">
-        <f t="shared" si="2"/>
-        <v>None</v>
-      </c>
-      <c r="I15">
+      <c r="H15">
         <v>2700</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -4094,25 +3743,21 @@
         <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G16">
         <v>5</v>
       </c>
-      <c r="H16" t="str">
-        <f t="shared" si="2"/>
-        <v>None</v>
-      </c>
-      <c r="I16">
+      <c r="H16">
         <v>810</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -4124,25 +3769,21 @@
         <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G17">
         <v>5</v>
       </c>
-      <c r="H17" t="str">
-        <f t="shared" si="2"/>
-        <v>None</v>
-      </c>
-      <c r="I17">
+      <c r="H17">
         <v>1500</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -4154,25 +3795,21 @@
         <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G18">
         <v>5</v>
       </c>
-      <c r="H18" t="str">
-        <f t="shared" si="2"/>
-        <v>None</v>
-      </c>
-      <c r="I18">
+      <c r="H18">
         <v>3300</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -4184,25 +3821,21 @@
         <v>5</v>
       </c>
       <c r="F19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G19">
         <v>5</v>
       </c>
-      <c r="H19" t="str">
-        <f t="shared" si="2"/>
-        <v>None</v>
-      </c>
-      <c r="I19">
+      <c r="H19">
         <v>800</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -4214,25 +3847,21 @@
         <v>5</v>
       </c>
       <c r="F20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G20">
         <v>5</v>
       </c>
-      <c r="H20" t="str">
-        <f t="shared" si="2"/>
-        <v>None</v>
-      </c>
-      <c r="I20">
+      <c r="H20">
         <v>1700</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -4244,25 +3873,21 @@
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G21">
         <v>5</v>
       </c>
-      <c r="H21" t="str">
-        <f t="shared" si="2"/>
-        <v>None</v>
-      </c>
-      <c r="I21">
+      <c r="H21">
         <v>10000</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -4275,16 +3900,12 @@
         <v>28</v>
       </c>
       <c r="F22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G22">
         <v>5</v>
       </c>
-      <c r="H22" t="str">
-        <f t="shared" si="2"/>
-        <v>None</v>
-      </c>
-      <c r="I22">
+      <c r="H22">
         <v>4000</v>
       </c>
     </row>
@@ -4497,33 +4118,33 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>115</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="E2" s="3">
         <v>0</v>
@@ -4531,16 +4152,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="E3" s="3">
         <v>1</v>
@@ -4548,16 +4169,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="E4" s="3">
         <v>2</v>
@@ -4565,16 +4186,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="E5" s="3">
         <v>3</v>

--- a/FPS_Test/Assets/Excel/ExcelData.xlsx
+++ b/FPS_Test/Assets/Excel/ExcelData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\GitHub\game_team\FPS_Test\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7992CADA-1C80-443E-865E-97306D204CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2C2D664-EEFB-4073-9712-7D0B255B2F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5865" yWindow="-11715" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5865" yWindow="-11715" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="common" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="141">
   <si>
     <t>id</t>
   </si>
@@ -922,6 +922,20 @@
   </si>
   <si>
     <t>RareArmor</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TreasureKey</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>宝箱の鍵</t>
+    <rPh sb="0" eb="2">
+      <t>タカラバコ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カギ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2806,7 +2820,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
@@ -3058,7 +3072,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>139</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -3067,16 +3081,16 @@
         <v>1</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="G10">
         <v>5</v>
       </c>
       <c r="H10">
-        <v>500</v>
+        <v>800</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.4">
@@ -3084,25 +3098,25 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G11">
         <v>5</v>
       </c>
       <c r="H11">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.4">
@@ -3110,25 +3124,25 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12">
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G12">
         <v>5</v>
       </c>
       <c r="H12">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.4">
@@ -3136,25 +3150,25 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13">
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G13">
         <v>5</v>
       </c>
       <c r="H13">
-        <v>1700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
@@ -3162,25 +3176,25 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14">
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G14">
         <v>5</v>
       </c>
       <c r="H14">
-        <v>620</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.4">
@@ -3188,25 +3202,25 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15">
         <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G15">
         <v>5</v>
       </c>
       <c r="H15">
-        <v>1500</v>
+        <v>620</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.4">
@@ -3214,25 +3228,25 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16">
         <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G16">
         <v>5</v>
       </c>
       <c r="H16">
-        <v>800</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.4">
@@ -3240,10 +3254,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -3252,7 +3266,7 @@
         <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -3266,25 +3280,25 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18">
         <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G18">
         <v>5</v>
       </c>
       <c r="H18">
-        <v>1200</v>
+        <v>800</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
@@ -3292,25 +3306,51 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19">
+        <v>5</v>
+      </c>
+      <c r="F19" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+      <c r="H19">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
         <v>58</v>
       </c>
-      <c r="C19">
-        <v>2</v>
-      </c>
-      <c r="D19">
-        <v>2</v>
-      </c>
-      <c r="E19">
-        <f>100-SUM(E2:E18)</f>
-        <v>39</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20">
+        <f>100-SUM(E2:E19)</f>
+        <v>37</v>
+      </c>
+      <c r="F20" t="s">
         <v>58</v>
       </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-      <c r="H19">
+      <c r="G20">
+        <v>5</v>
+      </c>
+      <c r="H20">
         <v>3000</v>
       </c>
     </row>

--- a/FPS_Test/Assets/Excel/ExcelData.xlsx
+++ b/FPS_Test/Assets/Excel/ExcelData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\GitHub\game_team\FPS_Test\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2C2D664-EEFB-4073-9712-7D0B255B2F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8DA7467-AA7E-4CE7-BE1E-1882BEC5B242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5865" yWindow="-11715" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3087,7 +3087,7 @@
         <v>140</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H10">
         <v>800</v>

--- a/FPS_Test/Assets/Excel/ExcelData.xlsx
+++ b/FPS_Test/Assets/Excel/ExcelData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\GitHub\game_team\FPS_Test\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8DA7467-AA7E-4CE7-BE1E-1882BEC5B242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D2A0E57-A291-4774-82A0-0EE375D58509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5865" yWindow="-11715" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="common" sheetId="1" r:id="rId1"/>
@@ -1377,7 +1377,7 @@
         <v>4</v>
       </c>
       <c r="H2">
-        <v>50</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1403,7 +1403,7 @@
         <v>4</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1429,7 +1429,7 @@
         <v>4</v>
       </c>
       <c r="H4">
-        <v>50</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -1455,7 +1455,7 @@
         <v>4</v>
       </c>
       <c r="H5">
-        <v>50</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -1975,7 +1975,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
@@ -2001,7 +2001,7 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
@@ -2027,7 +2027,7 @@
         <v>2</v>
       </c>
       <c r="H4">
-        <v>200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
@@ -2053,7 +2053,7 @@
         <v>3</v>
       </c>
       <c r="H5">
-        <v>200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
@@ -2079,7 +2079,7 @@
         <v>4</v>
       </c>
       <c r="H6">
-        <v>200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
@@ -2105,7 +2105,7 @@
         <v>4</v>
       </c>
       <c r="H7">
-        <v>200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
@@ -2131,7 +2131,7 @@
         <v>4</v>
       </c>
       <c r="H8">
-        <v>200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
@@ -2157,7 +2157,7 @@
         <v>4</v>
       </c>
       <c r="H9">
-        <v>200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
@@ -2882,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
@@ -2908,7 +2908,7 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
@@ -2934,7 +2934,7 @@
         <v>2</v>
       </c>
       <c r="H4">
-        <v>500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
@@ -2960,7 +2960,7 @@
         <v>3</v>
       </c>
       <c r="H5">
-        <v>500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
@@ -2986,7 +2986,7 @@
         <v>4</v>
       </c>
       <c r="H6">
-        <v>500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
@@ -3012,7 +3012,7 @@
         <v>4</v>
       </c>
       <c r="H7">
-        <v>500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
@@ -3038,7 +3038,7 @@
         <v>4</v>
       </c>
       <c r="H8">
-        <v>500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
@@ -3064,7 +3064,7 @@
         <v>4</v>
       </c>
       <c r="H9">
-        <v>500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>1000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
@@ -3451,7 +3451,7 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>1000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
@@ -3477,7 +3477,7 @@
         <v>2</v>
       </c>
       <c r="H4">
-        <v>1000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
@@ -3503,7 +3503,7 @@
         <v>3</v>
       </c>
       <c r="H5">
-        <v>1000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
@@ -3529,7 +3529,7 @@
         <v>4</v>
       </c>
       <c r="H6">
-        <v>1000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
@@ -3555,7 +3555,7 @@
         <v>4</v>
       </c>
       <c r="H7">
-        <v>1000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
@@ -3581,7 +3581,7 @@
         <v>4</v>
       </c>
       <c r="H8">
-        <v>1000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
@@ -3607,7 +3607,7 @@
         <v>4</v>
       </c>
       <c r="H9">
-        <v>1000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
